--- a/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>FUWAY</t>
   </si>
@@ -656,412 +656,426 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1704500</v>
+        <v>1767200</v>
       </c>
       <c r="E8" s="3">
-        <v>1636200</v>
+        <v>1730100</v>
       </c>
       <c r="F8" s="3">
-        <v>1861900</v>
+        <v>1660800</v>
       </c>
       <c r="G8" s="3">
-        <v>1735600</v>
+        <v>1889900</v>
       </c>
       <c r="H8" s="3">
-        <v>1754500</v>
+        <v>1761800</v>
       </c>
       <c r="I8" s="3">
-        <v>1728300</v>
+        <v>1780900</v>
       </c>
       <c r="J8" s="3">
+        <v>1754400</v>
+      </c>
+      <c r="K8" s="3">
         <v>1723500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1536700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1647100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1608300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1762400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1528700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1386100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1505900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2099200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2013000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2103900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2072600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2430900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2371300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2291000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2189100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2386100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2222700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2102500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2114700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1839400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1786300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1477900</v>
+        <v>1488100</v>
       </c>
       <c r="E9" s="3">
-        <v>1411400</v>
+        <v>1500200</v>
       </c>
       <c r="F9" s="3">
-        <v>1568200</v>
+        <v>1432600</v>
       </c>
       <c r="G9" s="3">
-        <v>1485200</v>
+        <v>1591900</v>
       </c>
       <c r="H9" s="3">
-        <v>1502600</v>
+        <v>1507600</v>
       </c>
       <c r="I9" s="3">
-        <v>1483800</v>
+        <v>1525200</v>
       </c>
       <c r="J9" s="3">
+        <v>1506200</v>
+      </c>
+      <c r="K9" s="3">
         <v>1471500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1328200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1394400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1348400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1477200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1277800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1174100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1270000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1756500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1673400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1754200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1742700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2038100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1933800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1917100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1828800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2011100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1840300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1727900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1665600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1714700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1490900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1461500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>226600</v>
+        <v>279000</v>
       </c>
       <c r="E10" s="3">
-        <v>224800</v>
+        <v>230000</v>
       </c>
       <c r="F10" s="3">
-        <v>293700</v>
+        <v>228200</v>
       </c>
       <c r="G10" s="3">
-        <v>250400</v>
+        <v>298100</v>
       </c>
       <c r="H10" s="3">
-        <v>251900</v>
+        <v>254200</v>
       </c>
       <c r="I10" s="3">
-        <v>244500</v>
+        <v>255700</v>
       </c>
       <c r="J10" s="3">
+        <v>248200</v>
+      </c>
+      <c r="K10" s="3">
         <v>252000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>208400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>252700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>259800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>285200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>250900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>212000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>235900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>342700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>339600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>349600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>330000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>392800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>437500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>373900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>360400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>375000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>382400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>374600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>367900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>400000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>348500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>324800</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1094,8 +1108,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1186,8 +1201,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1278,100 +1296,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-7000</v>
+        <v>3200</v>
       </c>
       <c r="E14" s="3">
-        <v>1400</v>
+        <v>-7100</v>
       </c>
       <c r="F14" s="3">
-        <v>23600</v>
+        <v>1500</v>
       </c>
       <c r="G14" s="3">
+        <v>24000</v>
+      </c>
+      <c r="H14" s="3">
+        <v>11000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L14" s="3">
+        <v>9200</v>
+      </c>
+      <c r="M14" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="N14" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="O14" s="3">
+        <v>23700</v>
+      </c>
+      <c r="P14" s="3">
+        <v>6300</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>12800</v>
+      </c>
+      <c r="R14" s="3">
+        <v>39500</v>
+      </c>
+      <c r="S14" s="3">
+        <v>12800</v>
+      </c>
+      <c r="T14" s="3">
         <v>8800</v>
       </c>
-      <c r="H14" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="J14" s="3">
-        <v>3300</v>
-      </c>
-      <c r="K14" s="3">
-        <v>9200</v>
-      </c>
-      <c r="L14" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="M14" s="3">
-        <v>-11900</v>
-      </c>
-      <c r="N14" s="3">
-        <v>23700</v>
-      </c>
-      <c r="O14" s="3">
-        <v>6300</v>
-      </c>
-      <c r="P14" s="3">
-        <v>12800</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>39500</v>
-      </c>
-      <c r="R14" s="3">
-        <v>12800</v>
-      </c>
-      <c r="S14" s="3">
-        <v>8800</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>13100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>40100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-3100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>106500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>22900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>142600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-45100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1462,8 +1486,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1493,192 +1520,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1709700</v>
+        <v>1743000</v>
       </c>
       <c r="E17" s="3">
-        <v>1656100</v>
+        <v>1735400</v>
       </c>
       <c r="F17" s="3">
-        <v>1823100</v>
+        <v>1681000</v>
       </c>
       <c r="G17" s="3">
-        <v>1734900</v>
+        <v>1850500</v>
       </c>
       <c r="H17" s="3">
-        <v>1733800</v>
+        <v>1759400</v>
       </c>
       <c r="I17" s="3">
-        <v>1718200</v>
+        <v>1759900</v>
       </c>
       <c r="J17" s="3">
+        <v>1744000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1684600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1560700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1617400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1568500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1721300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1515700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1415200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1556000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2039100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1980600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2063200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2034200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2373600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2244000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2208700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2114500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2388300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2141400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2002700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1941400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2125400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1701300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1727500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-5200</v>
+        <v>24100</v>
       </c>
       <c r="E18" s="3">
-        <v>-19900</v>
+        <v>-5300</v>
       </c>
       <c r="F18" s="3">
-        <v>38800</v>
+        <v>-20200</v>
       </c>
       <c r="G18" s="3">
-        <v>800</v>
+        <v>39400</v>
       </c>
       <c r="H18" s="3">
-        <v>20700</v>
+        <v>2400</v>
       </c>
       <c r="I18" s="3">
-        <v>10200</v>
+        <v>21000</v>
       </c>
       <c r="J18" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K18" s="3">
         <v>38900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-24000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>29700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>39700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>41100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-29100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-50100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>60100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>32400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>40700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>38400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>57300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>127300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>82300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>74600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>81300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>99800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>92100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-10700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>138000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1711,468 +1745,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>14500</v>
+        <v>-8800</v>
       </c>
       <c r="E20" s="3">
-        <v>39800</v>
+        <v>14700</v>
       </c>
       <c r="F20" s="3">
-        <v>27400</v>
+        <v>40400</v>
       </c>
       <c r="G20" s="3">
-        <v>66800</v>
+        <v>27800</v>
       </c>
       <c r="H20" s="3">
-        <v>15300</v>
+        <v>66100</v>
       </c>
       <c r="I20" s="3">
-        <v>50700</v>
+        <v>15500</v>
       </c>
       <c r="J20" s="3">
+        <v>51400</v>
+      </c>
+      <c r="K20" s="3">
         <v>31800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>13600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>15700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>21900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>69000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>162100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>87400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>18700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>27000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>10700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>10500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>25200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>11600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-15400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>13300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>36300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>75200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>13000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>18100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>73400</v>
+        <v>81600</v>
       </c>
       <c r="E21" s="3">
-        <v>83300</v>
+        <v>74500</v>
       </c>
       <c r="F21" s="3">
-        <v>135100</v>
+        <v>84600</v>
       </c>
       <c r="G21" s="3">
-        <v>132800</v>
+        <v>137100</v>
       </c>
       <c r="H21" s="3">
-        <v>99700</v>
+        <v>134600</v>
       </c>
       <c r="I21" s="3">
-        <v>122800</v>
+        <v>101200</v>
       </c>
       <c r="J21" s="3">
+        <v>124600</v>
+      </c>
+      <c r="K21" s="3">
         <v>122000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>51300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>106600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>124200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>164400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>78200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>16500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>179900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>211200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>124100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>131200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>115700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>126800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>219700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>152600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>120100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>66900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>177600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>228900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>155400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>51500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>212000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>117100</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>15300</v>
+        <v>16100</v>
       </c>
       <c r="E22" s="3">
-        <v>14500</v>
+        <v>15500</v>
       </c>
       <c r="F22" s="3">
-        <v>15200</v>
+        <v>14700</v>
       </c>
       <c r="G22" s="3">
-        <v>11200</v>
+        <v>15400</v>
       </c>
       <c r="H22" s="3">
-        <v>8900</v>
+        <v>11400</v>
       </c>
       <c r="I22" s="3">
-        <v>6800</v>
+        <v>9000</v>
       </c>
       <c r="J22" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K22" s="3">
         <v>6100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>5800</v>
       </c>
       <c r="M22" s="3">
         <v>5800</v>
       </c>
       <c r="N22" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="O22" s="3">
         <v>6200</v>
       </c>
       <c r="P22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="Q22" s="3">
         <v>7500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>9900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>10400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>10100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>10400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>10100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>8500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8900</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>9200</v>
       </c>
       <c r="AB22" s="3">
         <v>9200</v>
       </c>
       <c r="AC22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AD22" s="3">
         <v>8700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>7400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-6000</v>
+        <v>-800</v>
       </c>
       <c r="E23" s="3">
-        <v>5400</v>
+        <v>-6100</v>
       </c>
       <c r="F23" s="3">
-        <v>51100</v>
+        <v>5500</v>
       </c>
       <c r="G23" s="3">
-        <v>56400</v>
+        <v>51800</v>
       </c>
       <c r="H23" s="3">
-        <v>27100</v>
+        <v>57100</v>
       </c>
       <c r="I23" s="3">
-        <v>54000</v>
+        <v>27500</v>
       </c>
       <c r="J23" s="3">
+        <v>54900</v>
+      </c>
+      <c r="K23" s="3">
         <v>64700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>39500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>55800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>103900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-52200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>104300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>138700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>41100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>57300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>39000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>57400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>142400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>84800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>50700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>108400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>165800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>89500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>148700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>8100</v>
+        <v>11100</v>
       </c>
       <c r="E24" s="3">
-        <v>16000</v>
+        <v>8300</v>
       </c>
       <c r="F24" s="3">
-        <v>9000</v>
+        <v>16200</v>
       </c>
       <c r="G24" s="3">
-        <v>22800</v>
+        <v>9100</v>
       </c>
       <c r="H24" s="3">
-        <v>18100</v>
+        <v>23000</v>
       </c>
       <c r="I24" s="3">
-        <v>19100</v>
+        <v>18300</v>
       </c>
       <c r="J24" s="3">
+        <v>19400</v>
+      </c>
+      <c r="K24" s="3">
         <v>12000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>13800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>21000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>32600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>34400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>44600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>22400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>18700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>20100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-50000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>49000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>16600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>14000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>29400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>24400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>20700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-8200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>30600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2263,192 +2313,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-14200</v>
+        <v>-11900</v>
       </c>
       <c r="E26" s="3">
-        <v>-10600</v>
+        <v>-14400</v>
       </c>
       <c r="F26" s="3">
-        <v>42100</v>
+        <v>-10700</v>
       </c>
       <c r="G26" s="3">
-        <v>33700</v>
+        <v>42700</v>
       </c>
       <c r="H26" s="3">
-        <v>9100</v>
+        <v>34100</v>
       </c>
       <c r="I26" s="3">
-        <v>34900</v>
+        <v>9200</v>
       </c>
       <c r="J26" s="3">
+        <v>35400</v>
+      </c>
+      <c r="K26" s="3">
         <v>52700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>25800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>34800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>71300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>69900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>94200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>18700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>38600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>18800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>107400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>93400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>68200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>36700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>79000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>141400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>68700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>118000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-16200</v>
+        <v>-16000</v>
       </c>
       <c r="E27" s="3">
-        <v>-11300</v>
+        <v>-16400</v>
       </c>
       <c r="F27" s="3">
-        <v>36400</v>
+        <v>-11500</v>
       </c>
       <c r="G27" s="3">
-        <v>29800</v>
+        <v>36900</v>
       </c>
       <c r="H27" s="3">
-        <v>7000</v>
+        <v>30200</v>
       </c>
       <c r="I27" s="3">
-        <v>35000</v>
+        <v>7100</v>
       </c>
       <c r="J27" s="3">
+        <v>35500</v>
+      </c>
+      <c r="K27" s="3">
         <v>44800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>31100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>67600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-48800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>66800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>89800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>12400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>20800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>100200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>83500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>60700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>30100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>68100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>134300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>61800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-11700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>108400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2539,8 +2598,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2631,8 +2693,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2723,8 +2788,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2815,192 +2883,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-14500</v>
+        <v>8800</v>
       </c>
       <c r="E32" s="3">
-        <v>-39800</v>
+        <v>-14700</v>
       </c>
       <c r="F32" s="3">
-        <v>-27400</v>
+        <v>-40400</v>
       </c>
       <c r="G32" s="3">
-        <v>-66800</v>
+        <v>-27800</v>
       </c>
       <c r="H32" s="3">
-        <v>-15300</v>
+        <v>-66100</v>
       </c>
       <c r="I32" s="3">
-        <v>-50700</v>
+        <v>-15500</v>
       </c>
       <c r="J32" s="3">
+        <v>-51400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-31800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-13600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-15700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-21900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-69000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>15600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-162100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-87400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-18700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-27000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-10700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-10500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-25200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-11600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>15400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-13300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-36300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-75200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-16200</v>
+        <v>-16000</v>
       </c>
       <c r="E33" s="3">
-        <v>-11300</v>
+        <v>-16400</v>
       </c>
       <c r="F33" s="3">
-        <v>36400</v>
+        <v>-11500</v>
       </c>
       <c r="G33" s="3">
-        <v>29800</v>
+        <v>36900</v>
       </c>
       <c r="H33" s="3">
-        <v>7000</v>
+        <v>30200</v>
       </c>
       <c r="I33" s="3">
-        <v>35000</v>
+        <v>7100</v>
       </c>
       <c r="J33" s="3">
+        <v>35500</v>
+      </c>
+      <c r="K33" s="3">
         <v>44800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>31100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>67600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-48800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>66800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>89800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>12400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>20800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>100200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>83500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>60700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>30100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>68100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>134300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>61800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-11700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>108400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3091,197 +3168,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-16200</v>
+        <v>-16000</v>
       </c>
       <c r="E35" s="3">
-        <v>-11300</v>
+        <v>-16400</v>
       </c>
       <c r="F35" s="3">
-        <v>36400</v>
+        <v>-11500</v>
       </c>
       <c r="G35" s="3">
-        <v>29800</v>
+        <v>36900</v>
       </c>
       <c r="H35" s="3">
-        <v>7000</v>
+        <v>30200</v>
       </c>
       <c r="I35" s="3">
-        <v>35000</v>
+        <v>7100</v>
       </c>
       <c r="J35" s="3">
+        <v>35500</v>
+      </c>
+      <c r="K35" s="3">
         <v>44800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>31100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>67600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-48800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>66800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>89800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>12400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>20800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>100200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>83500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>60700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>30100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>68100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>134300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>61800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-11700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>108400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3314,8 +3400,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3348,163 +3435,167 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>357400</v>
+        <v>329900</v>
       </c>
       <c r="E41" s="3">
-        <v>370400</v>
+        <v>362800</v>
       </c>
       <c r="F41" s="3">
-        <v>314900</v>
+        <v>376000</v>
       </c>
       <c r="G41" s="3">
-        <v>387700</v>
+        <v>319700</v>
       </c>
       <c r="H41" s="3">
-        <v>410500</v>
+        <v>393500</v>
       </c>
       <c r="I41" s="3">
-        <v>390000</v>
+        <v>416700</v>
       </c>
       <c r="J41" s="3">
+        <v>395800</v>
+      </c>
+      <c r="K41" s="3">
         <v>432600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>442300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>385500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>641400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>598100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>559200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>637100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>962100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>478900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>346200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>368300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>395300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>428900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>442600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>445400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>374100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>457700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>471100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>479700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>390800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>418400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>496400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>415700</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>20300</v>
+        <v>27500</v>
       </c>
       <c r="E42" s="3">
-        <v>14300</v>
+        <v>20600</v>
       </c>
       <c r="F42" s="3">
-        <v>34000</v>
+        <v>14500</v>
       </c>
       <c r="G42" s="3">
-        <v>25300</v>
+        <v>34600</v>
       </c>
       <c r="H42" s="3">
-        <v>25600</v>
+        <v>25700</v>
       </c>
       <c r="I42" s="3">
-        <v>20800</v>
+        <v>25900</v>
       </c>
       <c r="J42" s="3">
+        <v>21100</v>
+      </c>
+      <c r="K42" s="3">
         <v>21600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>21500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>23600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>24700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>20700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>17100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>16500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>14000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>7900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>14100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>9300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>7400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>22800</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
@@ -3515,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="AA42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AB42" s="3">
         <v>300</v>
@@ -3524,660 +3615,684 @@
         <v>300</v>
       </c>
       <c r="AD42" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE42" s="3">
         <v>500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1499500</v>
+        <v>1518000</v>
       </c>
       <c r="E43" s="3">
-        <v>1504600</v>
+        <v>1522100</v>
       </c>
       <c r="F43" s="3">
-        <v>1515000</v>
+        <v>1527300</v>
       </c>
       <c r="G43" s="3">
-        <v>1474900</v>
+        <v>1537800</v>
       </c>
       <c r="H43" s="3">
-        <v>1519600</v>
+        <v>1497100</v>
       </c>
       <c r="I43" s="3">
-        <v>1546700</v>
+        <v>1542500</v>
       </c>
       <c r="J43" s="3">
+        <v>1570000</v>
+      </c>
+      <c r="K43" s="3">
         <v>1522400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1432200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1442100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1466200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1354400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1299400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1221000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1336000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1685000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1802000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1774400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1859900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2097400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2044600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2030100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1984900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2017000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2008900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1887000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1815800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1753000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1623600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1499600</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1246100</v>
+        <v>1309400</v>
       </c>
       <c r="E44" s="3">
-        <v>1237900</v>
+        <v>1264900</v>
       </c>
       <c r="F44" s="3">
-        <v>1144000</v>
+        <v>1256500</v>
       </c>
       <c r="G44" s="3">
-        <v>1283600</v>
+        <v>1161300</v>
       </c>
       <c r="H44" s="3">
-        <v>1209400</v>
+        <v>1302900</v>
       </c>
       <c r="I44" s="3">
-        <v>1212600</v>
+        <v>1227700</v>
       </c>
       <c r="J44" s="3">
+        <v>1230900</v>
+      </c>
+      <c r="K44" s="3">
         <v>1089700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1066000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1058500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1015000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>856700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>883600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>922000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1042700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1020700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1206600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1150600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1183100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1181000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1242300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1166900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1121800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1028700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1110200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1068000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1019900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>925600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>931400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>806700</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>245300</v>
+        <v>257900</v>
       </c>
       <c r="E45" s="3">
-        <v>254700</v>
+        <v>249000</v>
       </c>
       <c r="F45" s="3">
-        <v>224500</v>
+        <v>258500</v>
       </c>
       <c r="G45" s="3">
-        <v>253200</v>
+        <v>227800</v>
       </c>
       <c r="H45" s="3">
-        <v>234900</v>
+        <v>257000</v>
       </c>
       <c r="I45" s="3">
-        <v>253500</v>
+        <v>238400</v>
       </c>
       <c r="J45" s="3">
+        <v>257300</v>
+      </c>
+      <c r="K45" s="3">
         <v>273300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>252700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>225300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>270600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>217300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>224200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>204200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>248500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>209700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>250700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>245100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>262500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>311100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>260100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>243600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>229600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>348700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>316300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>301900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>300800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>294400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>325300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3368600</v>
+        <v>3442700</v>
       </c>
       <c r="E46" s="3">
-        <v>3381900</v>
+        <v>3419300</v>
       </c>
       <c r="F46" s="3">
-        <v>3232500</v>
+        <v>3432800</v>
       </c>
       <c r="G46" s="3">
-        <v>3424600</v>
+        <v>3281200</v>
       </c>
       <c r="H46" s="3">
-        <v>3399900</v>
+        <v>3476200</v>
       </c>
       <c r="I46" s="3">
-        <v>3423500</v>
+        <v>3451100</v>
       </c>
       <c r="J46" s="3">
+        <v>3475100</v>
+      </c>
+      <c r="K46" s="3">
         <v>3339700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3214700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3135000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3417800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3047400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2983400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3000900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3603300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3402200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3619700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3547700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3708100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4041100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3989700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3885900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3710500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3762400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3906800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3736800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3527600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3391900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3377000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3043500</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>829400</v>
+        <v>842000</v>
       </c>
       <c r="E47" s="3">
-        <v>796700</v>
+        <v>841900</v>
       </c>
       <c r="F47" s="3">
-        <v>1619000</v>
+        <v>808700</v>
       </c>
       <c r="G47" s="3">
-        <v>820700</v>
+        <v>1643300</v>
       </c>
       <c r="H47" s="3">
-        <v>853100</v>
+        <v>833000</v>
       </c>
       <c r="I47" s="3">
-        <v>822200</v>
+        <v>866000</v>
       </c>
       <c r="J47" s="3">
+        <v>834500</v>
+      </c>
+      <c r="K47" s="3">
         <v>809700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>755600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>772500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>768500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>777300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>789400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>774300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>838300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>936800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1090200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1066100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1062600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1193700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1158400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1237500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1200800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1239600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1221900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1137400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1096400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1162400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1059900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>986800</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1839700</v>
+        <v>1842800</v>
       </c>
       <c r="E48" s="3">
-        <v>1819900</v>
+        <v>1867400</v>
       </c>
       <c r="F48" s="3">
-        <v>2102400</v>
+        <v>1847300</v>
       </c>
       <c r="G48" s="3">
-        <v>1773500</v>
+        <v>2134100</v>
       </c>
       <c r="H48" s="3">
-        <v>1867600</v>
+        <v>1800200</v>
       </c>
       <c r="I48" s="3">
-        <v>1808700</v>
+        <v>1895700</v>
       </c>
       <c r="J48" s="3">
+        <v>1835900</v>
+      </c>
+      <c r="K48" s="3">
         <v>1727500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1729400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1818500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1839500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1749400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1786900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1943800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2118900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2239700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2274300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2257400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2213800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2204100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2093800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2081600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1996800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1959200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1941700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1933000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1907300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1822700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1766700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>131400</v>
+        <v>133000</v>
       </c>
       <c r="E49" s="3">
         <v>133400</v>
       </c>
       <c r="F49" s="3">
-        <v>134400</v>
+        <v>135400</v>
       </c>
       <c r="G49" s="3">
-        <v>130900</v>
+        <v>136400</v>
       </c>
       <c r="H49" s="3">
-        <v>133500</v>
+        <v>132900</v>
       </c>
       <c r="I49" s="3">
-        <v>134300</v>
+        <v>135600</v>
       </c>
       <c r="J49" s="3">
+        <v>136400</v>
+      </c>
+      <c r="K49" s="3">
         <v>136300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>135200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>143700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>149900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>143600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>142300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>146500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>146900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>141800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>128200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>122900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>113600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>117300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>95900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>92400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>90600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>102200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>96900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>87500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>86800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>86400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>79700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4268,8 +4383,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4360,100 +4478,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>251900</v>
+        <v>244800</v>
       </c>
       <c r="E52" s="3">
-        <v>252800</v>
+        <v>255700</v>
       </c>
       <c r="F52" s="3">
-        <v>255600</v>
+        <v>256600</v>
       </c>
       <c r="G52" s="3">
-        <v>241700</v>
+        <v>259400</v>
       </c>
       <c r="H52" s="3">
-        <v>254600</v>
+        <v>245300</v>
       </c>
       <c r="I52" s="3">
-        <v>255300</v>
+        <v>258400</v>
       </c>
       <c r="J52" s="3">
+        <v>259100</v>
+      </c>
+      <c r="K52" s="3">
         <v>201100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>237500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>249100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>254400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>181500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>232400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>260800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>290100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>280100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>304600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>339800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>338700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>304900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>273800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>279400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>276600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>301500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>261900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>263500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>260800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>190200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>240400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>259000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4544,100 +4668,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6421000</v>
+        <v>6505300</v>
       </c>
       <c r="E54" s="3">
-        <v>6384700</v>
+        <v>6517700</v>
       </c>
       <c r="F54" s="3">
-        <v>6198200</v>
+        <v>6480900</v>
       </c>
       <c r="G54" s="3">
-        <v>6391300</v>
+        <v>6291600</v>
       </c>
       <c r="H54" s="3">
-        <v>6508800</v>
+        <v>6487600</v>
       </c>
       <c r="I54" s="3">
-        <v>6444000</v>
+        <v>6606800</v>
       </c>
       <c r="J54" s="3">
+        <v>6541000</v>
+      </c>
+      <c r="K54" s="3">
         <v>6214200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6072400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6118800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6430100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5899200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5934500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6126200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6997500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7000600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7417000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7334000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7436800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7861200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7611600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7576800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7275300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7310000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7429200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7158200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6878900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6653600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6523700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6038700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4670,8 +4800,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4704,560 +4835,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>836400</v>
+        <v>854300</v>
       </c>
       <c r="E57" s="3">
-        <v>825100</v>
+        <v>849000</v>
       </c>
       <c r="F57" s="3">
-        <v>832700</v>
+        <v>837500</v>
       </c>
       <c r="G57" s="3">
-        <v>876600</v>
+        <v>845300</v>
       </c>
       <c r="H57" s="3">
-        <v>813000</v>
+        <v>889800</v>
       </c>
       <c r="I57" s="3">
-        <v>858200</v>
+        <v>825300</v>
       </c>
       <c r="J57" s="3">
+        <v>871200</v>
+      </c>
+      <c r="K57" s="3">
         <v>849800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>810900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>773200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>886600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>818900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>769800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>721600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>816700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>983100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1079200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1034700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1115500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1263000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1184200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1167500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1124900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1124500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1078800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1043900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>979900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>958700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>933000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>807800</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1246800</v>
+        <v>1281600</v>
       </c>
       <c r="E58" s="3">
-        <v>1247900</v>
+        <v>1265600</v>
       </c>
       <c r="F58" s="3">
-        <v>2079700</v>
+        <v>1266700</v>
       </c>
       <c r="G58" s="3">
-        <v>1275400</v>
+        <v>2111000</v>
       </c>
       <c r="H58" s="3">
-        <v>1292300</v>
+        <v>1294600</v>
       </c>
       <c r="I58" s="3">
-        <v>1218700</v>
+        <v>1311800</v>
       </c>
       <c r="J58" s="3">
+        <v>1237100</v>
+      </c>
+      <c r="K58" s="3">
         <v>1132500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1068800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>995600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1196900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>957400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1148400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1208100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1331600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1119500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1255200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1143000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1057800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1025500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1002200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1041000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>992900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2011900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1069900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1039900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1186800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>889700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>906300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>901000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>582800</v>
+        <v>566200</v>
       </c>
       <c r="E59" s="3">
-        <v>587500</v>
+        <v>591600</v>
       </c>
       <c r="F59" s="3">
-        <v>1082700</v>
+        <v>596300</v>
       </c>
       <c r="G59" s="3">
-        <v>559800</v>
+        <v>1099000</v>
       </c>
       <c r="H59" s="3">
-        <v>558500</v>
+        <v>568200</v>
       </c>
       <c r="I59" s="3">
-        <v>541500</v>
+        <v>566900</v>
       </c>
       <c r="J59" s="3">
+        <v>549600</v>
+      </c>
+      <c r="K59" s="3">
         <v>539000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>514400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>506000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>502700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>458500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>522400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>488300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>705500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>713500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>722800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>787200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>823100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>898400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>799400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>795000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>858300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>810600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>729400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>698800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>655700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>753700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>634400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>607500</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2666000</v>
+        <v>2702100</v>
       </c>
       <c r="E60" s="3">
-        <v>2660500</v>
+        <v>2706200</v>
       </c>
       <c r="F60" s="3">
-        <v>2530000</v>
+        <v>2700500</v>
       </c>
       <c r="G60" s="3">
-        <v>2711800</v>
+        <v>2568100</v>
       </c>
       <c r="H60" s="3">
-        <v>2663900</v>
+        <v>2752600</v>
       </c>
       <c r="I60" s="3">
-        <v>2618400</v>
+        <v>2704000</v>
       </c>
       <c r="J60" s="3">
+        <v>2657900</v>
+      </c>
+      <c r="K60" s="3">
         <v>2521300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2394100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2274800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2586200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2234800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2440600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2418100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2853900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2816100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3057300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2964900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2996400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3186900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2985700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3003400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2976100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2986200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2878200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2782600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2822400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2602100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2473700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2316200</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1033700</v>
+        <v>1097000</v>
       </c>
       <c r="E61" s="3">
-        <v>1026300</v>
+        <v>1049300</v>
       </c>
       <c r="F61" s="3">
-        <v>1026200</v>
+        <v>1041700</v>
       </c>
       <c r="G61" s="3">
-        <v>1030600</v>
+        <v>1041600</v>
       </c>
       <c r="H61" s="3">
-        <v>1095200</v>
+        <v>1046200</v>
       </c>
       <c r="I61" s="3">
-        <v>1157800</v>
+        <v>1111700</v>
       </c>
       <c r="J61" s="3">
+        <v>1175200</v>
+      </c>
+      <c r="K61" s="3">
         <v>1199900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1169700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1179800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1145000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1157000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>970100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1031400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1194200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1163200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1124300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1156800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1249500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1338700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1430100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1409800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1282300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1285700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1404900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1393400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1284400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1350300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1387100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1298000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>491200</v>
+        <v>479200</v>
       </c>
       <c r="E62" s="3">
-        <v>481300</v>
+        <v>498600</v>
       </c>
       <c r="F62" s="3">
-        <v>500800</v>
+        <v>488600</v>
       </c>
       <c r="G62" s="3">
-        <v>495100</v>
+        <v>508300</v>
       </c>
       <c r="H62" s="3">
-        <v>524600</v>
+        <v>502600</v>
       </c>
       <c r="I62" s="3">
-        <v>501100</v>
+        <v>532500</v>
       </c>
       <c r="J62" s="3">
+        <v>508700</v>
+      </c>
+      <c r="K62" s="3">
         <v>407600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>478000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>507200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>510600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>439800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>552700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>593100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>643000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>615900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>660700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>664500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>666500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>645700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>603400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>610100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>590600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>578600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>632000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>612200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>605000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>598500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>669800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>648200</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5348,8 +5498,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5440,8 +5593,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5532,100 +5688,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4378400</v>
+        <v>4470500</v>
       </c>
       <c r="E66" s="3">
-        <v>4350400</v>
+        <v>4444400</v>
       </c>
       <c r="F66" s="3">
-        <v>4195300</v>
+        <v>4416000</v>
       </c>
       <c r="G66" s="3">
-        <v>4417600</v>
+        <v>4258400</v>
       </c>
       <c r="H66" s="3">
-        <v>4527700</v>
+        <v>4484100</v>
       </c>
       <c r="I66" s="3">
-        <v>4513000</v>
+        <v>4595900</v>
       </c>
       <c r="J66" s="3">
+        <v>4580900</v>
+      </c>
+      <c r="K66" s="3">
         <v>4360200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4271800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4197300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4477200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4056700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4185300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4272000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4936700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4883700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5140700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5078600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5201600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5481200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5318700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5331200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5151200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5171900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5232100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5098300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4997900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4820100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4780100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4492300</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5658,8 +5820,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5750,8 +5913,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5842,8 +6008,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5934,8 +6103,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6026,100 +6198,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1209800</v>
+        <v>1212000</v>
       </c>
       <c r="E72" s="3">
-        <v>1226000</v>
+        <v>1228000</v>
       </c>
       <c r="F72" s="3">
-        <v>1273300</v>
+        <v>1244500</v>
       </c>
       <c r="G72" s="3">
-        <v>1217600</v>
+        <v>1292500</v>
       </c>
       <c r="H72" s="3">
-        <v>1187700</v>
+        <v>1235900</v>
       </c>
       <c r="I72" s="3">
-        <v>1173200</v>
+        <v>1205600</v>
       </c>
       <c r="J72" s="3">
+        <v>1190900</v>
+      </c>
+      <c r="K72" s="3">
         <v>1157700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1151000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1235200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1237500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1195000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1165500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1249000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1421000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1454500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1411200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1411100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1371500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1458300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1334100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1231100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1145200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1158300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1164400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1096400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>962100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>922000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>935100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>827300</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6210,8 +6388,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6302,8 +6483,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6394,100 +6578,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2042600</v>
+        <v>2034800</v>
       </c>
       <c r="E76" s="3">
-        <v>2034300</v>
+        <v>2073300</v>
       </c>
       <c r="F76" s="3">
-        <v>2003000</v>
+        <v>2064900</v>
       </c>
       <c r="G76" s="3">
-        <v>1973700</v>
+        <v>2033100</v>
       </c>
       <c r="H76" s="3">
-        <v>1981100</v>
+        <v>2003400</v>
       </c>
       <c r="I76" s="3">
-        <v>1931000</v>
+        <v>2011000</v>
       </c>
       <c r="J76" s="3">
+        <v>1960100</v>
+      </c>
+      <c r="K76" s="3">
         <v>1854000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1800600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1921500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1952900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1842500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1749200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1854200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2060800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2116900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2276300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2255400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2235100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2380000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2292900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2245600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2124100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2138100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2197100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2059900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1881000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1833500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1743600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1546400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6578,197 +6768,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-16200</v>
+        <v>-16000</v>
       </c>
       <c r="E81" s="3">
-        <v>-11300</v>
+        <v>-16400</v>
       </c>
       <c r="F81" s="3">
-        <v>36400</v>
+        <v>-11500</v>
       </c>
       <c r="G81" s="3">
-        <v>29800</v>
+        <v>36900</v>
       </c>
       <c r="H81" s="3">
-        <v>7000</v>
+        <v>30200</v>
       </c>
       <c r="I81" s="3">
-        <v>35000</v>
+        <v>7100</v>
       </c>
       <c r="J81" s="3">
+        <v>35500</v>
+      </c>
+      <c r="K81" s="3">
         <v>44800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>31100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>67600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-48800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>66800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>89800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>12400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>20800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>100200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>83500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>60700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>30100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>68100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>134300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>61800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-11700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>108400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6801,100 +7000,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>64200</v>
+        <v>66300</v>
       </c>
       <c r="E83" s="3">
+        <v>65100</v>
+      </c>
+      <c r="F83" s="3">
+        <v>64400</v>
+      </c>
+      <c r="G83" s="3">
+        <v>69900</v>
+      </c>
+      <c r="H83" s="3">
+        <v>66200</v>
+      </c>
+      <c r="I83" s="3">
+        <v>64600</v>
+      </c>
+      <c r="J83" s="3">
+        <v>62900</v>
+      </c>
+      <c r="K83" s="3">
+        <v>51300</v>
+      </c>
+      <c r="L83" s="3">
+        <v>61700</v>
+      </c>
+      <c r="M83" s="3">
+        <v>61300</v>
+      </c>
+      <c r="N83" s="3">
+        <v>62600</v>
+      </c>
+      <c r="O83" s="3">
+        <v>54300</v>
+      </c>
+      <c r="P83" s="3">
+        <v>63700</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>61200</v>
+      </c>
+      <c r="R83" s="3">
+        <v>67900</v>
+      </c>
+      <c r="S83" s="3">
+        <v>63700</v>
+      </c>
+      <c r="T83" s="3">
+        <v>73000</v>
+      </c>
+      <c r="U83" s="3">
         <v>63500</v>
       </c>
-      <c r="F83" s="3">
-        <v>68800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>65200</v>
-      </c>
-      <c r="H83" s="3">
-        <v>63700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>61900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>51300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>61700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>61300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>62600</v>
-      </c>
-      <c r="N83" s="3">
-        <v>54300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>63700</v>
-      </c>
-      <c r="P83" s="3">
-        <v>61200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>67900</v>
-      </c>
-      <c r="R83" s="3">
-        <v>63700</v>
-      </c>
-      <c r="S83" s="3">
-        <v>73000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>63500</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>66600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>59000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>67200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>58700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>60900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>55800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>60000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>53900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>57200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>49200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>55900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>49800</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6985,8 +7188,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7077,8 +7283,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7169,8 +7378,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7261,8 +7473,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7353,8 +7568,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7445,8 +7663,11 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7479,8 +7700,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7503,17 +7725,17 @@
         <v>-20784000</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-19927000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-24223000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -7571,8 +7793,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7663,8 +7888,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7755,8 +7983,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7847,8 +8078,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7881,8 +8115,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7973,8 +8208,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8065,8 +8303,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8157,8 +8398,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8249,8 +8493,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8341,8 +8588,11 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8433,8 +8683,11 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8523,6 +8776,9 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>FUWAY</t>
   </si>
@@ -656,426 +656,438 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1767200</v>
+        <v>1858000</v>
       </c>
       <c r="E8" s="3">
-        <v>1730100</v>
+        <v>1672800</v>
       </c>
       <c r="F8" s="3">
-        <v>1660800</v>
+        <v>1637700</v>
       </c>
       <c r="G8" s="3">
-        <v>1889900</v>
+        <v>1572100</v>
       </c>
       <c r="H8" s="3">
-        <v>1761800</v>
+        <v>1789000</v>
       </c>
       <c r="I8" s="3">
-        <v>1780900</v>
+        <v>1667700</v>
       </c>
       <c r="J8" s="3">
+        <v>1685800</v>
+      </c>
+      <c r="K8" s="3">
         <v>1754400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1723500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1536700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1647100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1608300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1762400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1528700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1386100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1505900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2099200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2013000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2103900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2072600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2430900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2371300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2291000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2189100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2386100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2222700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2102500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2114700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1839400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1786300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1488100</v>
+        <v>1541500</v>
       </c>
       <c r="E9" s="3">
-        <v>1500200</v>
+        <v>1408600</v>
       </c>
       <c r="F9" s="3">
-        <v>1432600</v>
+        <v>1420000</v>
       </c>
       <c r="G9" s="3">
-        <v>1591900</v>
+        <v>1356100</v>
       </c>
       <c r="H9" s="3">
-        <v>1507600</v>
+        <v>1506800</v>
       </c>
       <c r="I9" s="3">
-        <v>1525200</v>
+        <v>1427100</v>
       </c>
       <c r="J9" s="3">
+        <v>1443700</v>
+      </c>
+      <c r="K9" s="3">
         <v>1506200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1471500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1328200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1394400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1348400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1477200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1277800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1174100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1270000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1756500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1673400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1754200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1742700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2038100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1933800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1917100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1828800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2011100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1840300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1727900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1665600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1714700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1490900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1461500</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>279000</v>
+        <v>316500</v>
       </c>
       <c r="E10" s="3">
-        <v>230000</v>
+        <v>264100</v>
       </c>
       <c r="F10" s="3">
-        <v>228200</v>
+        <v>217700</v>
       </c>
       <c r="G10" s="3">
-        <v>298100</v>
+        <v>216000</v>
       </c>
       <c r="H10" s="3">
-        <v>254200</v>
+        <v>282200</v>
       </c>
       <c r="I10" s="3">
-        <v>255700</v>
+        <v>240600</v>
       </c>
       <c r="J10" s="3">
+        <v>242100</v>
+      </c>
+      <c r="K10" s="3">
         <v>248200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>252000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>208400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>252700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>259800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>285200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>250900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>212000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>235900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>342700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>339600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>349600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>330000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>392800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>437500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>373900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>360400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>375000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>382400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>374600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>367900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>400000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>348500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>324800</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1109,8 +1121,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1204,8 +1217,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,103 +1315,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>3200</v>
+        <v>6200</v>
       </c>
       <c r="E14" s="3">
-        <v>-7100</v>
+        <v>3000</v>
       </c>
       <c r="F14" s="3">
-        <v>1500</v>
+        <v>-6700</v>
       </c>
       <c r="G14" s="3">
-        <v>24000</v>
+        <v>1400</v>
       </c>
       <c r="H14" s="3">
-        <v>11000</v>
+        <v>42700</v>
       </c>
       <c r="I14" s="3">
-        <v>3500</v>
+        <v>10400</v>
       </c>
       <c r="J14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K14" s="3">
         <v>-1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-11900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>23700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>12800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>39500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>12800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>8800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>13100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>6600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>40100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>106500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>22900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>142600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-45100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1489,8 +1511,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1521,198 +1546,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1743000</v>
+        <v>1789400</v>
       </c>
       <c r="E17" s="3">
-        <v>1735400</v>
+        <v>1649900</v>
       </c>
       <c r="F17" s="3">
-        <v>1681000</v>
+        <v>1642700</v>
       </c>
       <c r="G17" s="3">
-        <v>1850500</v>
+        <v>1591200</v>
       </c>
       <c r="H17" s="3">
-        <v>1759400</v>
+        <v>1751700</v>
       </c>
       <c r="I17" s="3">
-        <v>1759900</v>
+        <v>1665400</v>
       </c>
       <c r="J17" s="3">
+        <v>1665900</v>
+      </c>
+      <c r="K17" s="3">
         <v>1744000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1684600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1560700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1617400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1568500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1721300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1515700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1415200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1556000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2039100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1980600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2063200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2034200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2373600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2244000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2208700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2114500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2388300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2141400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2002700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1941400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2125400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1701300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1727500</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>24100</v>
+        <v>68600</v>
       </c>
       <c r="E18" s="3">
-        <v>-5300</v>
+        <v>22800</v>
       </c>
       <c r="F18" s="3">
-        <v>-20200</v>
+        <v>-5000</v>
       </c>
       <c r="G18" s="3">
-        <v>39400</v>
+        <v>-19100</v>
       </c>
       <c r="H18" s="3">
-        <v>2400</v>
+        <v>37300</v>
       </c>
       <c r="I18" s="3">
-        <v>21000</v>
+        <v>2200</v>
       </c>
       <c r="J18" s="3">
+        <v>19900</v>
+      </c>
+      <c r="K18" s="3">
         <v>10300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>38900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>29700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>39700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>41100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-29100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-50100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>60100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>32400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>40700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>38400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>57300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>127300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>82300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>74600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>81300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>99800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>92100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-10700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>138000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1746,483 +1778,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-8800</v>
+        <v>75800</v>
       </c>
       <c r="E20" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F20" s="3">
+        <v>13900</v>
+      </c>
+      <c r="G20" s="3">
+        <v>38200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>23300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>62600</v>
+      </c>
+      <c r="J20" s="3">
         <v>14700</v>
       </c>
-      <c r="F20" s="3">
-        <v>40400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>27800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>66100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>15500</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>51400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>31800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>13600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>15700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>21900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>69000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-15600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>162100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>87400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>18700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>27000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>10700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>10500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>25200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>11600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-15400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>13300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>36300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>75200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>6100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>13000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>18100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>81600</v>
+        <v>207600</v>
       </c>
       <c r="E21" s="3">
-        <v>74500</v>
+        <v>77200</v>
       </c>
       <c r="F21" s="3">
-        <v>84600</v>
+        <v>70600</v>
       </c>
       <c r="G21" s="3">
-        <v>137100</v>
+        <v>80100</v>
       </c>
       <c r="H21" s="3">
-        <v>134600</v>
+        <v>126800</v>
       </c>
       <c r="I21" s="3">
-        <v>101200</v>
+        <v>127500</v>
       </c>
       <c r="J21" s="3">
+        <v>95800</v>
+      </c>
+      <c r="K21" s="3">
         <v>124600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>122000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>51300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>106600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>124200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>164400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>78200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>16500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>179900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>211200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>124100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>131200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>115700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>126800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>219700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>152600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>120100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>66900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>177600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>228900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>155400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>51500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>212000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>117100</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>16100</v>
+        <v>15100</v>
       </c>
       <c r="E22" s="3">
-        <v>15500</v>
+        <v>15200</v>
       </c>
       <c r="F22" s="3">
         <v>14700</v>
       </c>
       <c r="G22" s="3">
-        <v>15400</v>
+        <v>13900</v>
       </c>
       <c r="H22" s="3">
-        <v>11400</v>
+        <v>14600</v>
       </c>
       <c r="I22" s="3">
-        <v>9000</v>
+        <v>10700</v>
       </c>
       <c r="J22" s="3">
+        <v>8500</v>
+      </c>
+      <c r="K22" s="3">
         <v>6900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>5800</v>
       </c>
       <c r="N22" s="3">
         <v>5800</v>
       </c>
       <c r="O22" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="P22" s="3">
         <v>6200</v>
       </c>
       <c r="Q22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="R22" s="3">
         <v>7500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>10400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>10100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>10400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>10100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>9100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8900</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>9200</v>
       </c>
       <c r="AC22" s="3">
         <v>9200</v>
       </c>
       <c r="AD22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AE22" s="3">
         <v>8700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>7300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>129300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
-        <v>-6100</v>
-      </c>
       <c r="F23" s="3">
-        <v>5500</v>
+        <v>-5800</v>
       </c>
       <c r="G23" s="3">
-        <v>51800</v>
+        <v>5200</v>
       </c>
       <c r="H23" s="3">
-        <v>57100</v>
+        <v>46100</v>
       </c>
       <c r="I23" s="3">
-        <v>27500</v>
+        <v>54100</v>
       </c>
       <c r="J23" s="3">
+        <v>26100</v>
+      </c>
+      <c r="K23" s="3">
         <v>54900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>64700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>39500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>55800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>103900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-52200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>104300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>138700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>41100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>57300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>39000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>57400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>142400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>84800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>50700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>108400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>165800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>89500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>148700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>11100</v>
+        <v>40300</v>
       </c>
       <c r="E24" s="3">
-        <v>8300</v>
+        <v>10500</v>
       </c>
       <c r="F24" s="3">
-        <v>16200</v>
+        <v>7800</v>
       </c>
       <c r="G24" s="3">
-        <v>9100</v>
+        <v>15400</v>
       </c>
       <c r="H24" s="3">
-        <v>23000</v>
+        <v>8200</v>
       </c>
       <c r="I24" s="3">
-        <v>18300</v>
+        <v>21700</v>
       </c>
       <c r="J24" s="3">
+        <v>17400</v>
+      </c>
+      <c r="K24" s="3">
         <v>19400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>13800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>21000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>32600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>34400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>44600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>22400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>18700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>20100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-50000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>49000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>16600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>14000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>29400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>24400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>20700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>30600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2316,198 +2364,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-11900</v>
+        <v>89100</v>
       </c>
       <c r="E26" s="3">
-        <v>-14400</v>
+        <v>-11200</v>
       </c>
       <c r="F26" s="3">
-        <v>-10700</v>
+        <v>-13600</v>
       </c>
       <c r="G26" s="3">
-        <v>42700</v>
+        <v>-10200</v>
       </c>
       <c r="H26" s="3">
-        <v>34100</v>
+        <v>37900</v>
       </c>
       <c r="I26" s="3">
-        <v>9200</v>
+        <v>32300</v>
       </c>
       <c r="J26" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K26" s="3">
         <v>35400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>52700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>25800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>34800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>71300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-47000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>69900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>94200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>18700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>38600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>18800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>107400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>93400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>68200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>36700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>79000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>141400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>68700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>118000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-16000</v>
+        <v>83200</v>
       </c>
       <c r="E27" s="3">
-        <v>-16400</v>
+        <v>-15200</v>
       </c>
       <c r="F27" s="3">
-        <v>-11500</v>
+        <v>-15600</v>
       </c>
       <c r="G27" s="3">
-        <v>36900</v>
+        <v>-10900</v>
       </c>
       <c r="H27" s="3">
-        <v>30200</v>
+        <v>32400</v>
       </c>
       <c r="I27" s="3">
-        <v>7100</v>
+        <v>28600</v>
       </c>
       <c r="J27" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K27" s="3">
         <v>35500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>44800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>31100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>67600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-48800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>66800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>89800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>12400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>35100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>20800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>100200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>83500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>60700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>30100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>68100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>134300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>61800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-11700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>108400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2601,8 +2658,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2696,8 +2756,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2791,8 +2854,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2886,198 +2952,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>8800</v>
+        <v>-75800</v>
       </c>
       <c r="E32" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-62600</v>
+      </c>
+      <c r="J32" s="3">
         <v>-14700</v>
       </c>
-      <c r="F32" s="3">
-        <v>-40400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-27800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-66100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-15500</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-51400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-31800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-13600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-15700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-21900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-69000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>15600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-162100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-87400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-18700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-27000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-10700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-10500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-25200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-11600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>15400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-13300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-36300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-75200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-16000</v>
+        <v>83200</v>
       </c>
       <c r="E33" s="3">
-        <v>-16400</v>
+        <v>-15200</v>
       </c>
       <c r="F33" s="3">
-        <v>-11500</v>
+        <v>-15600</v>
       </c>
       <c r="G33" s="3">
-        <v>36900</v>
+        <v>-10900</v>
       </c>
       <c r="H33" s="3">
-        <v>30200</v>
+        <v>32400</v>
       </c>
       <c r="I33" s="3">
-        <v>7100</v>
+        <v>28600</v>
       </c>
       <c r="J33" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K33" s="3">
         <v>35500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>44800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>31100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>67600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-48800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>66800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>89800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>12400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>20800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>100200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>83500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>60700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>30100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>68100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>134300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>61800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-11700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>108400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3171,203 +3246,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-16000</v>
+        <v>83200</v>
       </c>
       <c r="E35" s="3">
-        <v>-16400</v>
+        <v>-15200</v>
       </c>
       <c r="F35" s="3">
-        <v>-11500</v>
+        <v>-15600</v>
       </c>
       <c r="G35" s="3">
-        <v>36900</v>
+        <v>-10900</v>
       </c>
       <c r="H35" s="3">
-        <v>30200</v>
+        <v>32400</v>
       </c>
       <c r="I35" s="3">
-        <v>7100</v>
+        <v>28600</v>
       </c>
       <c r="J35" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K35" s="3">
         <v>35500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>44800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>31100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>67600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-48800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>66800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>89800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>12400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>20800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>100200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>83500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>60700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>30100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>68100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>134300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>61800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-11700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>108400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3401,8 +3485,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3436,169 +3521,173 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>329900</v>
+        <v>312000</v>
       </c>
       <c r="E41" s="3">
-        <v>362800</v>
+        <v>312200</v>
       </c>
       <c r="F41" s="3">
-        <v>376000</v>
+        <v>343400</v>
       </c>
       <c r="G41" s="3">
-        <v>319700</v>
+        <v>355900</v>
       </c>
       <c r="H41" s="3">
-        <v>393500</v>
+        <v>302600</v>
       </c>
       <c r="I41" s="3">
-        <v>416700</v>
+        <v>372500</v>
       </c>
       <c r="J41" s="3">
+        <v>394400</v>
+      </c>
+      <c r="K41" s="3">
         <v>395800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>432600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>442300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>385500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>641400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>598100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>559200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>637100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>962100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>478900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>346200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>368300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>395300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>428900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>442600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>445400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>374100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>457700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>471100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>479700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>390800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>418400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>496400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>415700</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>27500</v>
+        <v>30300</v>
       </c>
       <c r="E42" s="3">
-        <v>20600</v>
+        <v>26100</v>
       </c>
       <c r="F42" s="3">
-        <v>14500</v>
+        <v>19500</v>
       </c>
       <c r="G42" s="3">
-        <v>34600</v>
+        <v>13700</v>
       </c>
       <c r="H42" s="3">
-        <v>25700</v>
+        <v>32700</v>
       </c>
       <c r="I42" s="3">
-        <v>25900</v>
+        <v>24300</v>
       </c>
       <c r="J42" s="3">
+        <v>24600</v>
+      </c>
+      <c r="K42" s="3">
         <v>21100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>21600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>21500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>23600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>24700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>20700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>17100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>16500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>14000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>7900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>14100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>9300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>7400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>22800</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
       <c r="Y42" s="3">
         <v>0</v>
       </c>
@@ -3609,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="AB42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AC42" s="3">
         <v>300</v>
@@ -3618,681 +3707,705 @@
         <v>300</v>
       </c>
       <c r="AE42" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF42" s="3">
         <v>500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1518000</v>
+        <v>1559900</v>
       </c>
       <c r="E43" s="3">
-        <v>1522100</v>
+        <v>1436900</v>
       </c>
       <c r="F43" s="3">
-        <v>1527300</v>
+        <v>1440800</v>
       </c>
       <c r="G43" s="3">
-        <v>1537800</v>
+        <v>1445700</v>
       </c>
       <c r="H43" s="3">
-        <v>1497100</v>
+        <v>1455700</v>
       </c>
       <c r="I43" s="3">
-        <v>1542500</v>
+        <v>1417200</v>
       </c>
       <c r="J43" s="3">
+        <v>1460100</v>
+      </c>
+      <c r="K43" s="3">
         <v>1570000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1522400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1432200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1442100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1466200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1354400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1299400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1221000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1336000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1685000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1802000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1774400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1859900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2097400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2044600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2030100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1984900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2017000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2008900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1887000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1815800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1753000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1623600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1499600</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1309400</v>
+        <v>1171700</v>
       </c>
       <c r="E44" s="3">
-        <v>1264900</v>
+        <v>1239500</v>
       </c>
       <c r="F44" s="3">
-        <v>1256500</v>
+        <v>1197300</v>
       </c>
       <c r="G44" s="3">
-        <v>1161300</v>
+        <v>1189400</v>
       </c>
       <c r="H44" s="3">
-        <v>1302900</v>
+        <v>1099200</v>
       </c>
       <c r="I44" s="3">
-        <v>1227700</v>
+        <v>1233300</v>
       </c>
       <c r="J44" s="3">
+        <v>1162100</v>
+      </c>
+      <c r="K44" s="3">
         <v>1230900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1089700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1066000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1058500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1015000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>856700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>883600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>922000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1042700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1020700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1206600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1150600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1183100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1181000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1242300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1166900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1121800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1028700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1110200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1068000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1019900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>925600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>931400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>806700</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>257900</v>
+        <v>229500</v>
       </c>
       <c r="E45" s="3">
-        <v>249000</v>
+        <v>244100</v>
       </c>
       <c r="F45" s="3">
-        <v>258500</v>
+        <v>235700</v>
       </c>
       <c r="G45" s="3">
-        <v>227800</v>
+        <v>244700</v>
       </c>
       <c r="H45" s="3">
-        <v>257000</v>
+        <v>215700</v>
       </c>
       <c r="I45" s="3">
-        <v>238400</v>
+        <v>243200</v>
       </c>
       <c r="J45" s="3">
+        <v>225700</v>
+      </c>
+      <c r="K45" s="3">
         <v>257300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>273300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>252700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>225300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>270600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>217300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>224200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>204200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>248500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>209700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>250700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>245100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>262500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>311100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>260100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>243600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>229600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>348700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>316300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>301900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>300800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>294400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>325300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3442700</v>
+        <v>3303400</v>
       </c>
       <c r="E46" s="3">
-        <v>3419300</v>
+        <v>3258800</v>
       </c>
       <c r="F46" s="3">
-        <v>3432800</v>
+        <v>3236700</v>
       </c>
       <c r="G46" s="3">
-        <v>3281200</v>
+        <v>3249500</v>
       </c>
       <c r="H46" s="3">
-        <v>3476200</v>
+        <v>3105900</v>
       </c>
       <c r="I46" s="3">
-        <v>3451100</v>
+        <v>3290500</v>
       </c>
       <c r="J46" s="3">
+        <v>3266800</v>
+      </c>
+      <c r="K46" s="3">
         <v>3475100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3339700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3214700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3135000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3417800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3047400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2983400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3000900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3603300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3402200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3619700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3547700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3708100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4041100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3989700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3885900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3710500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3762400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3906800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3736800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3527600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3391900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3377000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3043500</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>842000</v>
+        <v>842400</v>
       </c>
       <c r="E47" s="3">
-        <v>841900</v>
+        <v>797000</v>
       </c>
       <c r="F47" s="3">
-        <v>808700</v>
+        <v>796900</v>
       </c>
       <c r="G47" s="3">
-        <v>1643300</v>
+        <v>765500</v>
       </c>
       <c r="H47" s="3">
-        <v>833000</v>
+        <v>1555600</v>
       </c>
       <c r="I47" s="3">
-        <v>866000</v>
+        <v>788500</v>
       </c>
       <c r="J47" s="3">
+        <v>819700</v>
+      </c>
+      <c r="K47" s="3">
         <v>834500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>809700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>755600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>772500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>768500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>777300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>789400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>774300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>838300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>936800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1090200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1066100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1062600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1193700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1158400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1237500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1200800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1239600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1221900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1137400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1096400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1162400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1059900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>986800</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1842800</v>
+        <v>1777700</v>
       </c>
       <c r="E48" s="3">
-        <v>1867400</v>
+        <v>1744400</v>
       </c>
       <c r="F48" s="3">
-        <v>1847300</v>
+        <v>1767700</v>
       </c>
       <c r="G48" s="3">
-        <v>2134100</v>
+        <v>1748600</v>
       </c>
       <c r="H48" s="3">
-        <v>1800200</v>
+        <v>2020100</v>
       </c>
       <c r="I48" s="3">
-        <v>1895700</v>
+        <v>1704000</v>
       </c>
       <c r="J48" s="3">
+        <v>1794500</v>
+      </c>
+      <c r="K48" s="3">
         <v>1835900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1727500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1729400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1818500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1839500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1749400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1786900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1943800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2118900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2239700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2274300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2257400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2213800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2204100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2093800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2081600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1996800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1959200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1941700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1933000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1907300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1822700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1766700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>133000</v>
+        <v>129400</v>
       </c>
       <c r="E49" s="3">
-        <v>133400</v>
+        <v>125900</v>
       </c>
       <c r="F49" s="3">
-        <v>135400</v>
+        <v>126300</v>
       </c>
       <c r="G49" s="3">
+        <v>128200</v>
+      </c>
+      <c r="H49" s="3">
+        <v>129100</v>
+      </c>
+      <c r="I49" s="3">
+        <v>125800</v>
+      </c>
+      <c r="J49" s="3">
+        <v>128300</v>
+      </c>
+      <c r="K49" s="3">
         <v>136400</v>
       </c>
-      <c r="H49" s="3">
-        <v>132900</v>
-      </c>
-      <c r="I49" s="3">
-        <v>135600</v>
-      </c>
-      <c r="J49" s="3">
-        <v>136400</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>136300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>135200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>143700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>149900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>143600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>142300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>146500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>146900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>141800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>128200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>122900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>113600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>117300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>95900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>92400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>90600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>102200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>96900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>87500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>86800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>86400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>79700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4386,8 +4499,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,103 +4597,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>244800</v>
+        <v>231400</v>
       </c>
       <c r="E52" s="3">
-        <v>255700</v>
+        <v>231700</v>
       </c>
       <c r="F52" s="3">
-        <v>256600</v>
+        <v>242000</v>
       </c>
       <c r="G52" s="3">
-        <v>259400</v>
+        <v>242900</v>
       </c>
       <c r="H52" s="3">
-        <v>245300</v>
+        <v>245600</v>
       </c>
       <c r="I52" s="3">
-        <v>258400</v>
+        <v>232200</v>
       </c>
       <c r="J52" s="3">
+        <v>244600</v>
+      </c>
+      <c r="K52" s="3">
         <v>259100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>201100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>237500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>249100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>254400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>181500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>232400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>260800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>290100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>280100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>304600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>339800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>338700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>304900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>273800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>279400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>276600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>301500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>261900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>263500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>260800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>190200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>240400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>259000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4671,103 +4793,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6505300</v>
+        <v>6284300</v>
       </c>
       <c r="E54" s="3">
-        <v>6517700</v>
+        <v>6157800</v>
       </c>
       <c r="F54" s="3">
-        <v>6480900</v>
+        <v>6169500</v>
       </c>
       <c r="G54" s="3">
-        <v>6291600</v>
+        <v>6134700</v>
       </c>
       <c r="H54" s="3">
-        <v>6487600</v>
+        <v>5955500</v>
       </c>
       <c r="I54" s="3">
-        <v>6606800</v>
+        <v>6141100</v>
       </c>
       <c r="J54" s="3">
+        <v>6254000</v>
+      </c>
+      <c r="K54" s="3">
         <v>6541000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6214200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6072400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6118800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6430100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5899200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5934500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6126200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6997500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7000600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7417000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7334000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7436800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7861200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7611600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7576800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7275300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7310000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7429200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7158200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6878900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6653600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6523700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6038700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4801,8 +4929,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4836,578 +4965,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>854300</v>
+        <v>821600</v>
       </c>
       <c r="E57" s="3">
-        <v>849000</v>
+        <v>808600</v>
       </c>
       <c r="F57" s="3">
-        <v>837500</v>
+        <v>803600</v>
       </c>
       <c r="G57" s="3">
-        <v>845300</v>
+        <v>792800</v>
       </c>
       <c r="H57" s="3">
-        <v>889800</v>
+        <v>800100</v>
       </c>
       <c r="I57" s="3">
-        <v>825300</v>
+        <v>842200</v>
       </c>
       <c r="J57" s="3">
+        <v>781200</v>
+      </c>
+      <c r="K57" s="3">
         <v>871200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>849800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>810900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>773200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>886600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>818900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>769800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>721600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>816700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>983100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1079200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1034700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1115500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1263000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1184200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1167500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1124900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1124500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1078800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1043900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>979900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>958700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>933000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>807800</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1281600</v>
+        <v>1102900</v>
       </c>
       <c r="E58" s="3">
-        <v>1265600</v>
+        <v>1213200</v>
       </c>
       <c r="F58" s="3">
-        <v>1266700</v>
+        <v>1198000</v>
       </c>
       <c r="G58" s="3">
-        <v>2111000</v>
+        <v>1199100</v>
       </c>
       <c r="H58" s="3">
-        <v>1294600</v>
+        <v>1998200</v>
       </c>
       <c r="I58" s="3">
-        <v>1311800</v>
+        <v>1225500</v>
       </c>
       <c r="J58" s="3">
+        <v>1241700</v>
+      </c>
+      <c r="K58" s="3">
         <v>1237100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1132500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1068800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>995600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1196900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>957400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1148400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1208100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1331600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1119500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1255200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1143000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1057800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1025500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1002200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1041000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>992900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2011900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1069900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1039900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1186800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>889700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>906300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>901000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>566200</v>
+        <v>633200</v>
       </c>
       <c r="E59" s="3">
-        <v>591600</v>
+        <v>535900</v>
       </c>
       <c r="F59" s="3">
-        <v>596300</v>
+        <v>560000</v>
       </c>
       <c r="G59" s="3">
-        <v>1099000</v>
+        <v>564500</v>
       </c>
       <c r="H59" s="3">
-        <v>568200</v>
+        <v>1040300</v>
       </c>
       <c r="I59" s="3">
-        <v>566900</v>
+        <v>537900</v>
       </c>
       <c r="J59" s="3">
+        <v>536600</v>
+      </c>
+      <c r="K59" s="3">
         <v>549600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>539000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>514400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>506000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>502700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>458500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>522400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>488300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>705500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>713500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>722800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>787200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>823100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>898400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>799400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>795000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>858300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>810600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>729400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>698800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>655700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>753700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>634400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>607500</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2702100</v>
+        <v>2557700</v>
       </c>
       <c r="E60" s="3">
-        <v>2706200</v>
+        <v>2557700</v>
       </c>
       <c r="F60" s="3">
-        <v>2700500</v>
+        <v>2561600</v>
       </c>
       <c r="G60" s="3">
-        <v>2568100</v>
+        <v>2556300</v>
       </c>
       <c r="H60" s="3">
-        <v>2752600</v>
+        <v>2430900</v>
       </c>
       <c r="I60" s="3">
-        <v>2704000</v>
+        <v>2605600</v>
       </c>
       <c r="J60" s="3">
+        <v>2559600</v>
+      </c>
+      <c r="K60" s="3">
         <v>2657900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2521300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2394100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2274800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2586200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2234800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2440600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2418100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2853900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2816100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3057300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2964900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2996400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3186900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2985700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3003400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2976100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2986200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2878200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2782600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2822400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2602100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2473700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2316200</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1097000</v>
+        <v>1101700</v>
       </c>
       <c r="E61" s="3">
-        <v>1049300</v>
+        <v>1038400</v>
       </c>
       <c r="F61" s="3">
-        <v>1041700</v>
+        <v>993300</v>
       </c>
       <c r="G61" s="3">
-        <v>1041600</v>
+        <v>986100</v>
       </c>
       <c r="H61" s="3">
-        <v>1046200</v>
+        <v>986000</v>
       </c>
       <c r="I61" s="3">
-        <v>1111700</v>
+        <v>990300</v>
       </c>
       <c r="J61" s="3">
+        <v>1052400</v>
+      </c>
+      <c r="K61" s="3">
         <v>1175200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1199900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1169700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1179800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1145000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1157000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>970100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1031400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1194200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1163200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1124300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1156800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1249500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1338700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1430100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1409800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1282300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1285700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1404900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1393400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1284400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1350300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1387100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1298000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>479200</v>
+        <v>340600</v>
       </c>
       <c r="E62" s="3">
-        <v>498600</v>
+        <v>453600</v>
       </c>
       <c r="F62" s="3">
-        <v>488600</v>
+        <v>471900</v>
       </c>
       <c r="G62" s="3">
-        <v>508300</v>
+        <v>462500</v>
       </c>
       <c r="H62" s="3">
-        <v>502600</v>
+        <v>481200</v>
       </c>
       <c r="I62" s="3">
-        <v>532500</v>
+        <v>475700</v>
       </c>
       <c r="J62" s="3">
+        <v>504100</v>
+      </c>
+      <c r="K62" s="3">
         <v>508700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>407600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>478000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>507200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>510600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>439800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>552700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>593100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>643000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>615900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>660700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>664500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>666500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>645700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>603400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>610100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>590600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>578600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>632000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>612200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>605000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>598500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>669800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>648200</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5501,8 +5649,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5596,8 +5747,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5691,103 +5845,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4470500</v>
+        <v>4190900</v>
       </c>
       <c r="E66" s="3">
-        <v>4444400</v>
+        <v>4231700</v>
       </c>
       <c r="F66" s="3">
-        <v>4416000</v>
+        <v>4207000</v>
       </c>
       <c r="G66" s="3">
-        <v>4258400</v>
+        <v>4180100</v>
       </c>
       <c r="H66" s="3">
-        <v>4484100</v>
+        <v>4031000</v>
       </c>
       <c r="I66" s="3">
-        <v>4595900</v>
+        <v>4244600</v>
       </c>
       <c r="J66" s="3">
+        <v>4350400</v>
+      </c>
+      <c r="K66" s="3">
         <v>4580900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4360200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4271800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4197300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4477200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4056700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4185300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4272000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4936700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4883700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5140700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5078600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5201600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5481200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5318700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5331200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5151200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5171900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5232100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5098300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4997900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4820100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4780100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4492300</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5821,8 +5981,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5916,8 +6077,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6011,8 +6175,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6106,8 +6273,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6201,103 +6371,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1212000</v>
+        <v>1230400</v>
       </c>
       <c r="E72" s="3">
-        <v>1228000</v>
+        <v>1147300</v>
       </c>
       <c r="F72" s="3">
-        <v>1244500</v>
+        <v>1162400</v>
       </c>
       <c r="G72" s="3">
-        <v>1292500</v>
+        <v>1178000</v>
       </c>
       <c r="H72" s="3">
-        <v>1235900</v>
+        <v>1223400</v>
       </c>
       <c r="I72" s="3">
-        <v>1205600</v>
+        <v>1169900</v>
       </c>
       <c r="J72" s="3">
+        <v>1141200</v>
+      </c>
+      <c r="K72" s="3">
         <v>1190900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1157700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1151000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1235200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1237500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1195000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1165500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1249000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1421000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1454500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1411200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1411100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1371500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1458300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1334100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1231100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1145200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1158300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1164400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1096400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>962100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>922000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>935100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>827300</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6391,8 +6567,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6486,8 +6665,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6581,103 +6763,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2034800</v>
+        <v>2093400</v>
       </c>
       <c r="E76" s="3">
-        <v>2073300</v>
+        <v>1926100</v>
       </c>
       <c r="F76" s="3">
-        <v>2064900</v>
+        <v>1962600</v>
       </c>
       <c r="G76" s="3">
-        <v>2033100</v>
+        <v>1954600</v>
       </c>
       <c r="H76" s="3">
-        <v>2003400</v>
+        <v>1924500</v>
       </c>
       <c r="I76" s="3">
-        <v>2011000</v>
+        <v>1896400</v>
       </c>
       <c r="J76" s="3">
+        <v>1903600</v>
+      </c>
+      <c r="K76" s="3">
         <v>1960100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1854000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1800600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1921500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1952900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1842500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1749200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1854200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2060800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2116900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2276300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2255400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2235100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2380000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2292900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2245600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2124100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2138100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2197100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2059900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1881000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1833500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1743600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1546400</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6771,203 +6959,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-16000</v>
+        <v>83200</v>
       </c>
       <c r="E81" s="3">
-        <v>-16400</v>
+        <v>-15200</v>
       </c>
       <c r="F81" s="3">
-        <v>-11500</v>
+        <v>-15600</v>
       </c>
       <c r="G81" s="3">
-        <v>36900</v>
+        <v>-10900</v>
       </c>
       <c r="H81" s="3">
-        <v>30200</v>
+        <v>32400</v>
       </c>
       <c r="I81" s="3">
-        <v>7100</v>
+        <v>28600</v>
       </c>
       <c r="J81" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K81" s="3">
         <v>35500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>44800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>31100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>67600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-48800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>66800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>89800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>12400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>20800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>100200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>83500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>60700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>30100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>68100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>134300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>61800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-11700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>108400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7001,103 +7198,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>66300</v>
+        <v>63100</v>
       </c>
       <c r="E83" s="3">
-        <v>65100</v>
+        <v>62800</v>
       </c>
       <c r="F83" s="3">
-        <v>64400</v>
+        <v>61600</v>
       </c>
       <c r="G83" s="3">
-        <v>69900</v>
+        <v>61000</v>
       </c>
       <c r="H83" s="3">
-        <v>66200</v>
+        <v>66100</v>
       </c>
       <c r="I83" s="3">
-        <v>64600</v>
+        <v>62700</v>
       </c>
       <c r="J83" s="3">
+        <v>61200</v>
+      </c>
+      <c r="K83" s="3">
         <v>62900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>51300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>61700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>61300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>62600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>54300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>63700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>61200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>67900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>63700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>73000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>63500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>66600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>59000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>67200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>58700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>60900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>55800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>60000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>53900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>57200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>49200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>55900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>49800</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7191,8 +7392,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7286,8 +7490,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7381,8 +7588,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7476,8 +7686,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7571,8 +7784,11 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7666,8 +7882,11 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7701,44 +7920,45 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19053000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21210000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18921000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20335000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20698000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19316000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20784000</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-19927000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-24223000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -7796,8 +8016,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7891,8 +8114,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7986,8 +8212,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8081,8 +8310,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8116,8 +8348,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8211,8 +8444,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8306,8 +8542,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8401,8 +8640,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8496,8 +8738,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8591,8 +8836,11 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8686,8 +8934,11 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8779,6 +9030,9 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
@@ -798,25 +798,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1858000</v>
+        <v>2067700</v>
       </c>
       <c r="E8" s="3">
-        <v>1672800</v>
+        <v>1861500</v>
       </c>
       <c r="F8" s="3">
-        <v>1637700</v>
+        <v>1822500</v>
       </c>
       <c r="G8" s="3">
-        <v>1572100</v>
+        <v>1749500</v>
       </c>
       <c r="H8" s="3">
-        <v>1789000</v>
+        <v>1990900</v>
       </c>
       <c r="I8" s="3">
-        <v>1667700</v>
+        <v>1855900</v>
       </c>
       <c r="J8" s="3">
-        <v>1685800</v>
+        <v>1876100</v>
       </c>
       <c r="K8" s="3">
         <v>1754400</v>
@@ -896,25 +896,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1541500</v>
+        <v>1715500</v>
       </c>
       <c r="E9" s="3">
-        <v>1408600</v>
+        <v>1567600</v>
       </c>
       <c r="F9" s="3">
-        <v>1420000</v>
+        <v>1580300</v>
       </c>
       <c r="G9" s="3">
-        <v>1356100</v>
+        <v>1509100</v>
       </c>
       <c r="H9" s="3">
-        <v>1506800</v>
+        <v>1676900</v>
       </c>
       <c r="I9" s="3">
-        <v>1427100</v>
+        <v>1588100</v>
       </c>
       <c r="J9" s="3">
-        <v>1443700</v>
+        <v>1606700</v>
       </c>
       <c r="K9" s="3">
         <v>1506200</v>
@@ -994,25 +994,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>316500</v>
+        <v>352300</v>
       </c>
       <c r="E10" s="3">
-        <v>264100</v>
+        <v>293900</v>
       </c>
       <c r="F10" s="3">
-        <v>217700</v>
+        <v>242200</v>
       </c>
       <c r="G10" s="3">
-        <v>216000</v>
+        <v>240400</v>
       </c>
       <c r="H10" s="3">
-        <v>282200</v>
+        <v>314000</v>
       </c>
       <c r="I10" s="3">
-        <v>240600</v>
+        <v>267700</v>
       </c>
       <c r="J10" s="3">
-        <v>242100</v>
+        <v>269400</v>
       </c>
       <c r="K10" s="3">
         <v>248200</v>
@@ -1324,25 +1324,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>6200</v>
+        <v>6900</v>
       </c>
       <c r="E14" s="3">
-        <v>3000</v>
+        <v>3400</v>
       </c>
       <c r="F14" s="3">
-        <v>-6700</v>
+        <v>-7400</v>
       </c>
       <c r="G14" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="H14" s="3">
-        <v>42700</v>
+        <v>47500</v>
       </c>
       <c r="I14" s="3">
-        <v>10400</v>
+        <v>11600</v>
       </c>
       <c r="J14" s="3">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="K14" s="3">
         <v>-1500</v>
@@ -1553,25 +1553,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1789400</v>
+        <v>1991300</v>
       </c>
       <c r="E17" s="3">
-        <v>1649900</v>
+        <v>1836100</v>
       </c>
       <c r="F17" s="3">
-        <v>1642700</v>
+        <v>1828100</v>
       </c>
       <c r="G17" s="3">
-        <v>1591200</v>
+        <v>1770800</v>
       </c>
       <c r="H17" s="3">
-        <v>1751700</v>
+        <v>1949300</v>
       </c>
       <c r="I17" s="3">
-        <v>1665400</v>
+        <v>1853400</v>
       </c>
       <c r="J17" s="3">
-        <v>1665900</v>
+        <v>1853900</v>
       </c>
       <c r="K17" s="3">
         <v>1744000</v>
@@ -1651,25 +1651,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>68600</v>
+        <v>76400</v>
       </c>
       <c r="E18" s="3">
-        <v>22800</v>
+        <v>25400</v>
       </c>
       <c r="F18" s="3">
-        <v>-5000</v>
+        <v>-5600</v>
       </c>
       <c r="G18" s="3">
-        <v>-19100</v>
+        <v>-21300</v>
       </c>
       <c r="H18" s="3">
-        <v>37300</v>
+        <v>41500</v>
       </c>
       <c r="I18" s="3">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="J18" s="3">
-        <v>19900</v>
+        <v>22100</v>
       </c>
       <c r="K18" s="3">
         <v>10300</v>
@@ -1785,25 +1785,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>75800</v>
+        <v>84400</v>
       </c>
       <c r="E20" s="3">
-        <v>-8400</v>
+        <v>-9300</v>
       </c>
       <c r="F20" s="3">
-        <v>13900</v>
+        <v>15500</v>
       </c>
       <c r="G20" s="3">
-        <v>38200</v>
+        <v>42500</v>
       </c>
       <c r="H20" s="3">
-        <v>23300</v>
+        <v>26000</v>
       </c>
       <c r="I20" s="3">
-        <v>62600</v>
+        <v>69600</v>
       </c>
       <c r="J20" s="3">
-        <v>14700</v>
+        <v>16400</v>
       </c>
       <c r="K20" s="3">
         <v>51400</v>
@@ -1883,25 +1883,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>207600</v>
+        <v>231000</v>
       </c>
       <c r="E21" s="3">
-        <v>77200</v>
+        <v>86000</v>
       </c>
       <c r="F21" s="3">
-        <v>70600</v>
+        <v>78500</v>
       </c>
       <c r="G21" s="3">
-        <v>80100</v>
+        <v>89100</v>
       </c>
       <c r="H21" s="3">
-        <v>126800</v>
+        <v>141100</v>
       </c>
       <c r="I21" s="3">
-        <v>127500</v>
+        <v>141800</v>
       </c>
       <c r="J21" s="3">
-        <v>95800</v>
+        <v>106600</v>
       </c>
       <c r="K21" s="3">
         <v>124600</v>
@@ -1981,25 +1981,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>15100</v>
+        <v>16800</v>
       </c>
       <c r="E22" s="3">
-        <v>15200</v>
+        <v>17000</v>
       </c>
       <c r="F22" s="3">
-        <v>14700</v>
+        <v>16400</v>
       </c>
       <c r="G22" s="3">
-        <v>13900</v>
+        <v>15500</v>
       </c>
       <c r="H22" s="3">
-        <v>14600</v>
+        <v>16200</v>
       </c>
       <c r="I22" s="3">
-        <v>10700</v>
+        <v>12000</v>
       </c>
       <c r="J22" s="3">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="K22" s="3">
         <v>6900</v>
@@ -2079,25 +2079,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>129300</v>
+        <v>143900</v>
       </c>
       <c r="E23" s="3">
         <v>-800</v>
       </c>
       <c r="F23" s="3">
-        <v>-5800</v>
+        <v>-6400</v>
       </c>
       <c r="G23" s="3">
-        <v>5200</v>
+        <v>5800</v>
       </c>
       <c r="H23" s="3">
-        <v>46100</v>
+        <v>51300</v>
       </c>
       <c r="I23" s="3">
-        <v>54100</v>
+        <v>60200</v>
       </c>
       <c r="J23" s="3">
-        <v>26100</v>
+        <v>29000</v>
       </c>
       <c r="K23" s="3">
         <v>54900</v>
@@ -2177,25 +2177,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>40300</v>
+        <v>44800</v>
       </c>
       <c r="E24" s="3">
-        <v>10500</v>
+        <v>11700</v>
       </c>
       <c r="F24" s="3">
-        <v>7800</v>
+        <v>8700</v>
       </c>
       <c r="G24" s="3">
-        <v>15400</v>
+        <v>17100</v>
       </c>
       <c r="H24" s="3">
-        <v>8200</v>
+        <v>9100</v>
       </c>
       <c r="I24" s="3">
-        <v>21700</v>
+        <v>24200</v>
       </c>
       <c r="J24" s="3">
-        <v>17400</v>
+        <v>19300</v>
       </c>
       <c r="K24" s="3">
         <v>19400</v>
@@ -2373,25 +2373,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>89100</v>
+        <v>99100</v>
       </c>
       <c r="E26" s="3">
-        <v>-11200</v>
+        <v>-12500</v>
       </c>
       <c r="F26" s="3">
-        <v>-13600</v>
+        <v>-15100</v>
       </c>
       <c r="G26" s="3">
-        <v>-10200</v>
+        <v>-11300</v>
       </c>
       <c r="H26" s="3">
-        <v>37900</v>
+        <v>42200</v>
       </c>
       <c r="I26" s="3">
-        <v>32300</v>
+        <v>35900</v>
       </c>
       <c r="J26" s="3">
-        <v>8700</v>
+        <v>9700</v>
       </c>
       <c r="K26" s="3">
         <v>35400</v>
@@ -2471,25 +2471,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>83200</v>
+        <v>92500</v>
       </c>
       <c r="E27" s="3">
-        <v>-15200</v>
+        <v>-16900</v>
       </c>
       <c r="F27" s="3">
-        <v>-15600</v>
+        <v>-17300</v>
       </c>
       <c r="G27" s="3">
-        <v>-10900</v>
+        <v>-12100</v>
       </c>
       <c r="H27" s="3">
-        <v>32400</v>
+        <v>36100</v>
       </c>
       <c r="I27" s="3">
-        <v>28600</v>
+        <v>31900</v>
       </c>
       <c r="J27" s="3">
-        <v>6700</v>
+        <v>7500</v>
       </c>
       <c r="K27" s="3">
         <v>35500</v>
@@ -2961,25 +2961,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-75800</v>
+        <v>-84400</v>
       </c>
       <c r="E32" s="3">
-        <v>8400</v>
+        <v>9300</v>
       </c>
       <c r="F32" s="3">
-        <v>-13900</v>
+        <v>-15500</v>
       </c>
       <c r="G32" s="3">
-        <v>-38200</v>
+        <v>-42500</v>
       </c>
       <c r="H32" s="3">
-        <v>-23300</v>
+        <v>-26000</v>
       </c>
       <c r="I32" s="3">
-        <v>-62600</v>
+        <v>-69600</v>
       </c>
       <c r="J32" s="3">
-        <v>-14700</v>
+        <v>-16400</v>
       </c>
       <c r="K32" s="3">
         <v>-51400</v>
@@ -3059,25 +3059,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>83200</v>
+        <v>92500</v>
       </c>
       <c r="E33" s="3">
-        <v>-15200</v>
+        <v>-16900</v>
       </c>
       <c r="F33" s="3">
-        <v>-15600</v>
+        <v>-17300</v>
       </c>
       <c r="G33" s="3">
-        <v>-10900</v>
+        <v>-12100</v>
       </c>
       <c r="H33" s="3">
-        <v>32400</v>
+        <v>36100</v>
       </c>
       <c r="I33" s="3">
-        <v>28600</v>
+        <v>31900</v>
       </c>
       <c r="J33" s="3">
-        <v>6700</v>
+        <v>7500</v>
       </c>
       <c r="K33" s="3">
         <v>35500</v>
@@ -3255,25 +3255,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>83200</v>
+        <v>92500</v>
       </c>
       <c r="E35" s="3">
-        <v>-15200</v>
+        <v>-16900</v>
       </c>
       <c r="F35" s="3">
-        <v>-15600</v>
+        <v>-17300</v>
       </c>
       <c r="G35" s="3">
-        <v>-10900</v>
+        <v>-12100</v>
       </c>
       <c r="H35" s="3">
-        <v>32400</v>
+        <v>36100</v>
       </c>
       <c r="I35" s="3">
-        <v>28600</v>
+        <v>31900</v>
       </c>
       <c r="J35" s="3">
-        <v>6700</v>
+        <v>7500</v>
       </c>
       <c r="K35" s="3">
         <v>35500</v>
@@ -3528,25 +3528,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>312000</v>
+        <v>347200</v>
       </c>
       <c r="E41" s="3">
-        <v>312200</v>
+        <v>347500</v>
       </c>
       <c r="F41" s="3">
-        <v>343400</v>
+        <v>382200</v>
       </c>
       <c r="G41" s="3">
-        <v>355900</v>
+        <v>396100</v>
       </c>
       <c r="H41" s="3">
-        <v>302600</v>
+        <v>336800</v>
       </c>
       <c r="I41" s="3">
-        <v>372500</v>
+        <v>414600</v>
       </c>
       <c r="J41" s="3">
-        <v>394400</v>
+        <v>438900</v>
       </c>
       <c r="K41" s="3">
         <v>395800</v>
@@ -3626,25 +3626,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>30300</v>
+        <v>33700</v>
       </c>
       <c r="E42" s="3">
-        <v>26100</v>
+        <v>29000</v>
       </c>
       <c r="F42" s="3">
-        <v>19500</v>
+        <v>21700</v>
       </c>
       <c r="G42" s="3">
-        <v>13700</v>
+        <v>15300</v>
       </c>
       <c r="H42" s="3">
-        <v>32700</v>
+        <v>36400</v>
       </c>
       <c r="I42" s="3">
-        <v>24300</v>
+        <v>27000</v>
       </c>
       <c r="J42" s="3">
-        <v>24600</v>
+        <v>27300</v>
       </c>
       <c r="K42" s="3">
         <v>21100</v>
@@ -3724,25 +3724,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1559900</v>
+        <v>1736000</v>
       </c>
       <c r="E43" s="3">
-        <v>1436900</v>
+        <v>1599100</v>
       </c>
       <c r="F43" s="3">
-        <v>1440800</v>
+        <v>1603400</v>
       </c>
       <c r="G43" s="3">
-        <v>1445700</v>
+        <v>1608900</v>
       </c>
       <c r="H43" s="3">
-        <v>1455700</v>
+        <v>1619900</v>
       </c>
       <c r="I43" s="3">
-        <v>1417200</v>
+        <v>1577100</v>
       </c>
       <c r="J43" s="3">
-        <v>1460100</v>
+        <v>1624800</v>
       </c>
       <c r="K43" s="3">
         <v>1570000</v>
@@ -3822,25 +3822,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1171700</v>
+        <v>1303900</v>
       </c>
       <c r="E44" s="3">
-        <v>1239500</v>
+        <v>1379400</v>
       </c>
       <c r="F44" s="3">
-        <v>1197300</v>
+        <v>1332400</v>
       </c>
       <c r="G44" s="3">
-        <v>1189400</v>
+        <v>1323700</v>
       </c>
       <c r="H44" s="3">
-        <v>1099200</v>
+        <v>1223300</v>
       </c>
       <c r="I44" s="3">
-        <v>1233300</v>
+        <v>1372500</v>
       </c>
       <c r="J44" s="3">
-        <v>1162100</v>
+        <v>1293200</v>
       </c>
       <c r="K44" s="3">
         <v>1230900</v>
@@ -3920,25 +3920,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>229500</v>
+        <v>255400</v>
       </c>
       <c r="E45" s="3">
-        <v>244100</v>
+        <v>271600</v>
       </c>
       <c r="F45" s="3">
-        <v>235700</v>
+        <v>262300</v>
       </c>
       <c r="G45" s="3">
-        <v>244700</v>
+        <v>272300</v>
       </c>
       <c r="H45" s="3">
-        <v>215700</v>
+        <v>240000</v>
       </c>
       <c r="I45" s="3">
-        <v>243200</v>
+        <v>270700</v>
       </c>
       <c r="J45" s="3">
-        <v>225700</v>
+        <v>251100</v>
       </c>
       <c r="K45" s="3">
         <v>257300</v>
@@ -4018,25 +4018,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3303400</v>
+        <v>3676100</v>
       </c>
       <c r="E46" s="3">
-        <v>3258800</v>
+        <v>3626600</v>
       </c>
       <c r="F46" s="3">
-        <v>3236700</v>
+        <v>3602000</v>
       </c>
       <c r="G46" s="3">
-        <v>3249500</v>
+        <v>3616200</v>
       </c>
       <c r="H46" s="3">
-        <v>3105900</v>
+        <v>3456400</v>
       </c>
       <c r="I46" s="3">
-        <v>3290500</v>
+        <v>3661900</v>
       </c>
       <c r="J46" s="3">
-        <v>3266800</v>
+        <v>3635500</v>
       </c>
       <c r="K46" s="3">
         <v>3475100</v>
@@ -4116,25 +4116,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>842400</v>
+        <v>937500</v>
       </c>
       <c r="E47" s="3">
-        <v>797000</v>
+        <v>886900</v>
       </c>
       <c r="F47" s="3">
-        <v>796900</v>
+        <v>886800</v>
       </c>
       <c r="G47" s="3">
-        <v>765500</v>
+        <v>851900</v>
       </c>
       <c r="H47" s="3">
-        <v>1555600</v>
+        <v>1721400</v>
       </c>
       <c r="I47" s="3">
-        <v>788500</v>
+        <v>877500</v>
       </c>
       <c r="J47" s="3">
-        <v>819700</v>
+        <v>912200</v>
       </c>
       <c r="K47" s="3">
         <v>834500</v>
@@ -4214,25 +4214,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1777700</v>
+        <v>1978300</v>
       </c>
       <c r="E48" s="3">
-        <v>1744400</v>
+        <v>1941200</v>
       </c>
       <c r="F48" s="3">
-        <v>1767700</v>
+        <v>1967200</v>
       </c>
       <c r="G48" s="3">
-        <v>1748600</v>
+        <v>1946000</v>
       </c>
       <c r="H48" s="3">
-        <v>2020100</v>
+        <v>2411800</v>
       </c>
       <c r="I48" s="3">
-        <v>1704000</v>
+        <v>1896300</v>
       </c>
       <c r="J48" s="3">
-        <v>1794500</v>
+        <v>1997000</v>
       </c>
       <c r="K48" s="3">
         <v>1835900</v>
@@ -4312,25 +4312,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>129400</v>
+        <v>144000</v>
       </c>
       <c r="E49" s="3">
-        <v>125900</v>
+        <v>140100</v>
       </c>
       <c r="F49" s="3">
-        <v>126300</v>
+        <v>140500</v>
       </c>
       <c r="G49" s="3">
-        <v>128200</v>
+        <v>142600</v>
       </c>
       <c r="H49" s="3">
-        <v>129100</v>
+        <v>143700</v>
       </c>
       <c r="I49" s="3">
-        <v>125800</v>
+        <v>140000</v>
       </c>
       <c r="J49" s="3">
-        <v>128300</v>
+        <v>142800</v>
       </c>
       <c r="K49" s="3">
         <v>136400</v>
@@ -4606,25 +4606,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>231400</v>
+        <v>257500</v>
       </c>
       <c r="E52" s="3">
-        <v>231700</v>
+        <v>257900</v>
       </c>
       <c r="F52" s="3">
-        <v>242000</v>
+        <v>269300</v>
       </c>
       <c r="G52" s="3">
-        <v>242900</v>
+        <v>270400</v>
       </c>
       <c r="H52" s="3">
-        <v>245600</v>
+        <v>243000</v>
       </c>
       <c r="I52" s="3">
-        <v>232200</v>
+        <v>258400</v>
       </c>
       <c r="J52" s="3">
-        <v>244600</v>
+        <v>272200</v>
       </c>
       <c r="K52" s="3">
         <v>259100</v>
@@ -4802,25 +4802,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6284300</v>
+        <v>6993500</v>
       </c>
       <c r="E54" s="3">
-        <v>6157800</v>
+        <v>6852700</v>
       </c>
       <c r="F54" s="3">
-        <v>6169500</v>
+        <v>6865800</v>
       </c>
       <c r="G54" s="3">
-        <v>6134700</v>
+        <v>6827100</v>
       </c>
       <c r="H54" s="3">
-        <v>5955500</v>
+        <v>6627600</v>
       </c>
       <c r="I54" s="3">
-        <v>6141100</v>
+        <v>6834100</v>
       </c>
       <c r="J54" s="3">
-        <v>6254000</v>
+        <v>6959700</v>
       </c>
       <c r="K54" s="3">
         <v>6541000</v>
@@ -4972,25 +4972,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>821600</v>
+        <v>914300</v>
       </c>
       <c r="E57" s="3">
-        <v>808600</v>
+        <v>899900</v>
       </c>
       <c r="F57" s="3">
-        <v>803600</v>
+        <v>894300</v>
       </c>
       <c r="G57" s="3">
-        <v>792800</v>
+        <v>882200</v>
       </c>
       <c r="H57" s="3">
-        <v>800100</v>
+        <v>890400</v>
       </c>
       <c r="I57" s="3">
-        <v>842200</v>
+        <v>937300</v>
       </c>
       <c r="J57" s="3">
-        <v>781200</v>
+        <v>869400</v>
       </c>
       <c r="K57" s="3">
         <v>871200</v>
@@ -5070,25 +5070,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1102900</v>
+        <v>1251300</v>
       </c>
       <c r="E58" s="3">
-        <v>1213200</v>
+        <v>1350100</v>
       </c>
       <c r="F58" s="3">
-        <v>1198000</v>
+        <v>1333200</v>
       </c>
       <c r="G58" s="3">
-        <v>1199100</v>
+        <v>1334400</v>
       </c>
       <c r="H58" s="3">
-        <v>1998200</v>
+        <v>2223700</v>
       </c>
       <c r="I58" s="3">
-        <v>1225500</v>
+        <v>1363800</v>
       </c>
       <c r="J58" s="3">
-        <v>1241700</v>
+        <v>1381900</v>
       </c>
       <c r="K58" s="3">
         <v>1237100</v>
@@ -5168,25 +5168,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>633200</v>
+        <v>680700</v>
       </c>
       <c r="E59" s="3">
-        <v>535900</v>
+        <v>596400</v>
       </c>
       <c r="F59" s="3">
-        <v>560000</v>
+        <v>623200</v>
       </c>
       <c r="G59" s="3">
-        <v>564500</v>
+        <v>628200</v>
       </c>
       <c r="H59" s="3">
-        <v>1040300</v>
+        <v>1157700</v>
       </c>
       <c r="I59" s="3">
-        <v>537900</v>
+        <v>598600</v>
       </c>
       <c r="J59" s="3">
-        <v>536600</v>
+        <v>597200</v>
       </c>
       <c r="K59" s="3">
         <v>549600</v>
@@ -5266,25 +5266,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2557700</v>
+        <v>2846300</v>
       </c>
       <c r="E60" s="3">
-        <v>2557700</v>
+        <v>2846400</v>
       </c>
       <c r="F60" s="3">
-        <v>2561600</v>
+        <v>2850700</v>
       </c>
       <c r="G60" s="3">
-        <v>2556300</v>
+        <v>2844800</v>
       </c>
       <c r="H60" s="3">
-        <v>2430900</v>
+        <v>2705300</v>
       </c>
       <c r="I60" s="3">
-        <v>2605600</v>
+        <v>2899600</v>
       </c>
       <c r="J60" s="3">
-        <v>2559600</v>
+        <v>2848400</v>
       </c>
       <c r="K60" s="3">
         <v>2657900</v>
@@ -5364,25 +5364,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1101700</v>
+        <v>1226100</v>
       </c>
       <c r="E61" s="3">
-        <v>1038400</v>
+        <v>1155600</v>
       </c>
       <c r="F61" s="3">
-        <v>993300</v>
+        <v>1105400</v>
       </c>
       <c r="G61" s="3">
-        <v>986100</v>
+        <v>1097400</v>
       </c>
       <c r="H61" s="3">
-        <v>986000</v>
+        <v>1186400</v>
       </c>
       <c r="I61" s="3">
-        <v>990300</v>
+        <v>1102000</v>
       </c>
       <c r="J61" s="3">
-        <v>1052400</v>
+        <v>1171100</v>
       </c>
       <c r="K61" s="3">
         <v>1175200</v>
@@ -5462,25 +5462,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>340600</v>
+        <v>379100</v>
       </c>
       <c r="E62" s="3">
-        <v>453600</v>
+        <v>504800</v>
       </c>
       <c r="F62" s="3">
-        <v>471900</v>
+        <v>525200</v>
       </c>
       <c r="G62" s="3">
-        <v>462500</v>
+        <v>514700</v>
       </c>
       <c r="H62" s="3">
-        <v>481200</v>
+        <v>446400</v>
       </c>
       <c r="I62" s="3">
-        <v>475700</v>
+        <v>529400</v>
       </c>
       <c r="J62" s="3">
-        <v>504100</v>
+        <v>561000</v>
       </c>
       <c r="K62" s="3">
         <v>508700</v>
@@ -5854,25 +5854,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4190900</v>
+        <v>4663900</v>
       </c>
       <c r="E66" s="3">
-        <v>4231700</v>
+        <v>4709300</v>
       </c>
       <c r="F66" s="3">
-        <v>4207000</v>
+        <v>4681700</v>
       </c>
       <c r="G66" s="3">
-        <v>4180100</v>
+        <v>4651800</v>
       </c>
       <c r="H66" s="3">
-        <v>4031000</v>
+        <v>4485900</v>
       </c>
       <c r="I66" s="3">
-        <v>4244600</v>
+        <v>4723600</v>
       </c>
       <c r="J66" s="3">
-        <v>4350400</v>
+        <v>4841300</v>
       </c>
       <c r="K66" s="3">
         <v>4580900</v>
@@ -6380,25 +6380,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1230400</v>
+        <v>1369300</v>
       </c>
       <c r="E72" s="3">
-        <v>1147300</v>
+        <v>1276700</v>
       </c>
       <c r="F72" s="3">
-        <v>1162400</v>
+        <v>1293600</v>
       </c>
       <c r="G72" s="3">
-        <v>1178000</v>
+        <v>1310900</v>
       </c>
       <c r="H72" s="3">
-        <v>1223400</v>
+        <v>1361500</v>
       </c>
       <c r="I72" s="3">
-        <v>1169900</v>
+        <v>1301900</v>
       </c>
       <c r="J72" s="3">
-        <v>1141200</v>
+        <v>1270000</v>
       </c>
       <c r="K72" s="3">
         <v>1190900</v>
@@ -6772,25 +6772,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2093400</v>
+        <v>2329700</v>
       </c>
       <c r="E76" s="3">
-        <v>1926100</v>
+        <v>2143500</v>
       </c>
       <c r="F76" s="3">
-        <v>1962600</v>
+        <v>2184100</v>
       </c>
       <c r="G76" s="3">
-        <v>1954600</v>
+        <v>2175200</v>
       </c>
       <c r="H76" s="3">
-        <v>1924500</v>
+        <v>2141700</v>
       </c>
       <c r="I76" s="3">
-        <v>1896400</v>
+        <v>2110500</v>
       </c>
       <c r="J76" s="3">
-        <v>1903600</v>
+        <v>2118400</v>
       </c>
       <c r="K76" s="3">
         <v>1960100</v>
@@ -7071,25 +7071,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>83200</v>
+        <v>92500</v>
       </c>
       <c r="E81" s="3">
-        <v>-15200</v>
+        <v>-16900</v>
       </c>
       <c r="F81" s="3">
-        <v>-15600</v>
+        <v>-17300</v>
       </c>
       <c r="G81" s="3">
-        <v>-10900</v>
+        <v>-12100</v>
       </c>
       <c r="H81" s="3">
-        <v>32400</v>
+        <v>36100</v>
       </c>
       <c r="I81" s="3">
-        <v>28600</v>
+        <v>31900</v>
       </c>
       <c r="J81" s="3">
-        <v>6700</v>
+        <v>7500</v>
       </c>
       <c r="K81" s="3">
         <v>35500</v>
@@ -7205,25 +7205,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>63100</v>
+        <v>70300</v>
       </c>
       <c r="E83" s="3">
-        <v>62800</v>
+        <v>69800</v>
       </c>
       <c r="F83" s="3">
-        <v>61600</v>
+        <v>68600</v>
       </c>
       <c r="G83" s="3">
-        <v>61000</v>
+        <v>67900</v>
       </c>
       <c r="H83" s="3">
-        <v>66100</v>
+        <v>73600</v>
       </c>
       <c r="I83" s="3">
-        <v>62700</v>
+        <v>69700</v>
       </c>
       <c r="J83" s="3">
-        <v>61200</v>
+        <v>68100</v>
       </c>
       <c r="K83" s="3">
         <v>62900</v>

--- a/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>FUWAY</t>
   </si>
@@ -656,438 +656,468 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>2067700</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1861500</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1822500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1749500</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1990900</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>1855900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1876100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1754400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1723500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1536700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1647100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1608300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1762400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1528700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1386100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1505900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2099200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2013000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2103900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2072600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2430900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2371300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2291000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2189100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>2386100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2222700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2102500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2114700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>1839400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>1786300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>1715500</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1567600</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1580300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1509100</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1676900</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>1588100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1606700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1506200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1471500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1328200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1394400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1348400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1477200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1277800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1174100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1270000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1756500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1673400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1754200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1742700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2038100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1933800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1917100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1828800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2011100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1840300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1727900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1665600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1714700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>1490900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>1461500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>352300</v>
-      </c>
-      <c r="E10" s="3">
-        <v>293900</v>
-      </c>
-      <c r="F10" s="3">
-        <v>242200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>240400</v>
-      </c>
-      <c r="H10" s="3">
-        <v>314000</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>267700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>269400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>248200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>252000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>208400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>252700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>259800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>285200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>250900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>212000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>235900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>342700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>339600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>349600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>330000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>392800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>437500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>373900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>360400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>375000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>382400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>374600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>367900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>400000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>348500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>324800</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1122,8 +1152,10 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1220,8 +1252,14 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,129 +1356,141 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>6900</v>
-      </c>
-      <c r="E14" s="3">
-        <v>3400</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H14" s="3">
-        <v>47500</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>11600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>3700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-1500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>3300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>9200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-4700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-11900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>23700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>6300</v>
-      </c>
-      <c r="R14" s="3">
-        <v>12800</v>
-      </c>
-      <c r="S14" s="3">
-        <v>39500</v>
       </c>
       <c r="T14" s="3">
         <v>12800</v>
       </c>
       <c r="U14" s="3">
+        <v>39500</v>
+      </c>
+      <c r="V14" s="3">
+        <v>12800</v>
+      </c>
+      <c r="W14" s="3">
         <v>8800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>13100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>6600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>40100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>1600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>2800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>106500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>22900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>2500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>2200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>142600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>-45100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1514,8 +1564,14 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1547,204 +1603,218 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>1991300</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1836100</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1828100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1770800</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1949300</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>1853400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1853900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1744000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1684600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1560700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1617400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1568500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1721300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1515700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1415200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1556000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2039100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1980600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2063200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2034200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2373600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2244000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2208700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2114500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2388300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2141400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2002700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1941400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2125400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>1701300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>1727500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>76400</v>
-      </c>
-      <c r="E18" s="3">
-        <v>25400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-21300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>41500</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>2500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>22100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>10300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>38900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-24000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>29700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>39700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>41100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>13000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-29100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-50100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>60100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>32400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>40700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>38400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>57300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>127300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>82300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>74600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>81300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>99800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>92100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-10700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>138000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1779,266 +1849,280 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>84400</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>15500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>42500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>26000</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>69600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>16400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>51400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>31800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>13600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>15700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>21900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>69000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>1500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-15600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>162100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>87400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>18700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>27000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>10700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>10500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>25200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>11600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-15400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>13300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>36300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>75200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>6100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>13000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>18100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>231000</v>
-      </c>
-      <c r="E21" s="3">
-        <v>86000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>78500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>89100</v>
-      </c>
-      <c r="H21" s="3">
-        <v>141100</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>141800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>106600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>124600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>122000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>51300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>106600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>124200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>164400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>78200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>16500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>179900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>211200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>124100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>131200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>115700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>126800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>219700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>152600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>120100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>66900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>177600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>228900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>155400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>51500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>212000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>117100</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>16800</v>
-      </c>
-      <c r="E22" s="3">
-        <v>17000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>16400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>15500</v>
-      </c>
-      <c r="H22" s="3">
-        <v>16200</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>12000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>9500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>6900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>6100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>6000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>5800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>5800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>6200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>6200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>7500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>7700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>8800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>9900</v>
-      </c>
-      <c r="V22" s="3">
-        <v>10400</v>
-      </c>
-      <c r="W22" s="3">
-        <v>10100</v>
       </c>
       <c r="X22" s="3">
         <v>10400</v>
@@ -2047,230 +2131,248 @@
         <v>10100</v>
       </c>
       <c r="Z22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>10100</v>
+      </c>
+      <c r="AB22" s="3">
         <v>9100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>8500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>8900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>9200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>9200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>8700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>7300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>7400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>143900</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-800</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-6400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>51300</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>60200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>29000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>54900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>64700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-16400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>39500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>55800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>103900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>8300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-52200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>104300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>138700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>41100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>57300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>39000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>57400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>142400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>84800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>50700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>2200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>108400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>165800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>89500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>148700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>44800</v>
-      </c>
-      <c r="E24" s="3">
-        <v>11700</v>
-      </c>
-      <c r="F24" s="3">
-        <v>8700</v>
-      </c>
-      <c r="G24" s="3">
-        <v>17100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>9100</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>24200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>19300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>19400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>12000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>4200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>13800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>21000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>32600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>9200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-5200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>34400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>44600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>22400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>18700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>20100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>49000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>16600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>14000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>29400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>24400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>20700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-8200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>30600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2367,204 +2469,222 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>99100</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-12500</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-15100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-11300</v>
-      </c>
-      <c r="H26" s="3">
-        <v>42200</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>35900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>9700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>35400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>52700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-20600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>25800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>34800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>71300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-47000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>69900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>94200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>18700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>38600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>18800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>107400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>93400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>68200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>36700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>2900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>79000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>141400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>68700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>3300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>118000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>92500</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-16900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="H27" s="3">
-        <v>36100</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>31900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>7500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>35500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>44800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-26500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>21400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>31100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>67600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-8100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-48800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>66800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>89800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>12400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>35100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>20800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>100200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>83500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>60700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>30100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>68100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>134300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>61800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-11700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>108400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2661,31 +2781,37 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2759,8 +2885,14 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2857,8 +2989,14 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2955,204 +3093,222 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-84400</v>
-      </c>
-      <c r="E32" s="3">
-        <v>9300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-15500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-42500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-26000</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-69600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-16400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-51400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-31800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-13600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-15700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-21900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-69000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-1500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>15600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-162100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-87400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-18700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-27000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-10700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-25200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>15400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-13300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-36300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-75200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>92500</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-16900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>36100</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>31900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>7500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>35500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>44800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-26500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>21400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>31100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>67600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-8100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-48800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>66800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>89800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>12400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>35100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>20800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>100200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>83500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>60700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>30100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>68100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>134300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>61800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-11700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>108400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3249,209 +3405,227 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>92500</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-16900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>36100</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>31900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>7500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>35500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>44800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-26500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>21400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>31100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>67600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-8100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-48800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>66800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>89800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>12400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>35100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>20800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>100200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>83500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>60700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>30100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>68100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>134300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>61800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-11700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>108400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3486,8 +3660,10 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3522,178 +3698,186 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>361200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>270300</v>
+      </c>
+      <c r="F41" s="3">
+        <v>323300</v>
+      </c>
+      <c r="G41" s="3">
         <v>347200</v>
       </c>
-      <c r="E41" s="3">
-        <v>347500</v>
-      </c>
-      <c r="F41" s="3">
-        <v>382200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>396100</v>
-      </c>
       <c r="H41" s="3">
-        <v>336800</v>
+        <v>360400</v>
       </c>
       <c r="I41" s="3">
+        <v>385800</v>
+      </c>
+      <c r="J41" s="3">
+        <v>356800</v>
+      </c>
+      <c r="K41" s="3">
         <v>414600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>438900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>395800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>432600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>442300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>385500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>641400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>598100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>559200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>637100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>962100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>478900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>346200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>368300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>395300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>428900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>442600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>445400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>374100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>457700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>471100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>479700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>390800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>418400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>496400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>415700</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>33700</v>
+        <v>38000</v>
       </c>
       <c r="E42" s="3">
+        <v>25300</v>
+      </c>
+      <c r="F42" s="3">
+        <v>31400</v>
+      </c>
+      <c r="G42" s="3">
         <v>29000</v>
       </c>
-      <c r="F42" s="3">
-        <v>21700</v>
-      </c>
-      <c r="G42" s="3">
-        <v>15300</v>
-      </c>
       <c r="H42" s="3">
-        <v>36400</v>
+        <v>20400</v>
       </c>
       <c r="I42" s="3">
+        <v>14900</v>
+      </c>
+      <c r="J42" s="3">
+        <v>38600</v>
+      </c>
+      <c r="K42" s="3">
         <v>27000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>27300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>21100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>21600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>21500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>23600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>24700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>20700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>17100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>16500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>14000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>7900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>14100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>9300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>7400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>22800</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="3">
-        <v>0</v>
-      </c>
       <c r="AA42" s="3">
         <v>0</v>
       </c>
@@ -3701,711 +3885,759 @@
         <v>0</v>
       </c>
       <c r="AC42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AD42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AE42" s="3">
         <v>300</v>
       </c>
       <c r="AF42" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH42" s="3">
         <v>500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1736000</v>
+        <v>1715900</v>
       </c>
       <c r="E43" s="3">
-        <v>1599100</v>
+        <v>1534800</v>
       </c>
       <c r="F43" s="3">
-        <v>1603400</v>
+        <v>1616500</v>
       </c>
       <c r="G43" s="3">
-        <v>1608900</v>
+        <v>1597800</v>
       </c>
       <c r="H43" s="3">
-        <v>1619900</v>
+        <v>1512000</v>
       </c>
       <c r="I43" s="3">
+        <v>1567300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1716300</v>
+      </c>
+      <c r="K43" s="3">
         <v>1577100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1624800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1570000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1522400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1432200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1442100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1466200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1354400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1299400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1221000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1336000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1685000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1802000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1774400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1859900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2097400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2044600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2030100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1984900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>2017000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>2008900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1887000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>1815800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>1753000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>1623600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>1499600</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1303900</v>
+        <v>1370400</v>
       </c>
       <c r="E44" s="3">
-        <v>1379400</v>
+        <v>1244600</v>
       </c>
       <c r="F44" s="3">
-        <v>1332400</v>
+        <v>1214100</v>
       </c>
       <c r="G44" s="3">
-        <v>1323700</v>
+        <v>1378200</v>
       </c>
       <c r="H44" s="3">
-        <v>1223300</v>
+        <v>1256500</v>
       </c>
       <c r="I44" s="3">
+        <v>1289400</v>
+      </c>
+      <c r="J44" s="3">
+        <v>1296100</v>
+      </c>
+      <c r="K44" s="3">
         <v>1372500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1293200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1230900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1089700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1066000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1058500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1015000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>856700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>883600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>922000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1042700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1020700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1206600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>1150600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1183100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1181000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1242300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1166900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1121800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1028700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1110200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1068000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1019900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>925600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>931400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>806700</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>255400</v>
+        <v>251900</v>
       </c>
       <c r="E45" s="3">
-        <v>271600</v>
+        <v>236100</v>
       </c>
       <c r="F45" s="3">
-        <v>262300</v>
+        <v>237900</v>
       </c>
       <c r="G45" s="3">
-        <v>272300</v>
+        <v>271400</v>
       </c>
       <c r="H45" s="3">
-        <v>240000</v>
+        <v>247300</v>
       </c>
       <c r="I45" s="3">
+        <v>265300</v>
+      </c>
+      <c r="J45" s="3">
+        <v>254300</v>
+      </c>
+      <c r="K45" s="3">
         <v>270700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>251100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>257300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>273300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>252700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>225300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>270600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>217300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>224200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>204200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>248500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>209700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>250700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>245100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>262500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>311100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>260100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>243600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>229600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>348700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>316300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>301900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>300800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>294400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>325300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3676100</v>
+        <v>3737500</v>
       </c>
       <c r="E46" s="3">
-        <v>3626600</v>
+        <v>3311100</v>
       </c>
       <c r="F46" s="3">
-        <v>3602000</v>
+        <v>3423100</v>
       </c>
       <c r="G46" s="3">
-        <v>3616200</v>
+        <v>3623600</v>
       </c>
       <c r="H46" s="3">
-        <v>3456400</v>
+        <v>3396600</v>
       </c>
       <c r="I46" s="3">
+        <v>3522700</v>
+      </c>
+      <c r="J46" s="3">
+        <v>3662100</v>
+      </c>
+      <c r="K46" s="3">
         <v>3661900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3635500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3475100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3339700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3214700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3135000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3417800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3047400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2983400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>3000900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3603300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3402200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3619700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3547700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3708100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4041100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>3989700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3885900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>3710500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3762400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>3906800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>3736800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>3527600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>3391900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>3377000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>3043500</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>937500</v>
+        <v>956200</v>
       </c>
       <c r="E47" s="3">
-        <v>886900</v>
+        <v>799600</v>
       </c>
       <c r="F47" s="3">
-        <v>886800</v>
+        <v>1056200</v>
       </c>
       <c r="G47" s="3">
-        <v>851900</v>
+        <v>1076800</v>
       </c>
       <c r="H47" s="3">
-        <v>1721400</v>
+        <v>1024500</v>
       </c>
       <c r="I47" s="3">
+        <v>1027400</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1121300</v>
+      </c>
+      <c r="K47" s="3">
         <v>877500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>912200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>834500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>809700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>755600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>772500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>768500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>777300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>789400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>774300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>838300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>936800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1090200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1066100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1062600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1193700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1158400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>1237500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>1200800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>1239600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>1221900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>1137400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>1096400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>1162400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>1059900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>986800</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1978300</v>
+        <v>1911300</v>
       </c>
       <c r="E48" s="3">
-        <v>1941200</v>
+        <v>1751200</v>
       </c>
       <c r="F48" s="3">
-        <v>1967200</v>
+        <v>1842200</v>
       </c>
       <c r="G48" s="3">
-        <v>1946000</v>
+        <v>1939600</v>
       </c>
       <c r="H48" s="3">
-        <v>2411800</v>
+        <v>1855000</v>
       </c>
       <c r="I48" s="3">
+        <v>1895600</v>
+      </c>
+      <c r="J48" s="3">
+        <v>2025700</v>
+      </c>
+      <c r="K48" s="3">
         <v>1896300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1997000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1835900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1727500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1729400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1818500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1839500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1749400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1786900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1943800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2118900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2239700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2274300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2257400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2213800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2204100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2093800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2081600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1996800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1959200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1941700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1933000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1907300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1822700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1766700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>144000</v>
+        <v>139800</v>
       </c>
       <c r="E49" s="3">
-        <v>140100</v>
+        <v>123800</v>
       </c>
       <c r="F49" s="3">
-        <v>140500</v>
+        <v>134100</v>
       </c>
       <c r="G49" s="3">
-        <v>142600</v>
+        <v>140000</v>
       </c>
       <c r="H49" s="3">
+        <v>132500</v>
+      </c>
+      <c r="I49" s="3">
+        <v>138900</v>
+      </c>
+      <c r="J49" s="3">
+        <v>152200</v>
+      </c>
+      <c r="K49" s="3">
+        <v>140000</v>
+      </c>
+      <c r="L49" s="3">
+        <v>142800</v>
+      </c>
+      <c r="M49" s="3">
+        <v>136400</v>
+      </c>
+      <c r="N49" s="3">
+        <v>136300</v>
+      </c>
+      <c r="O49" s="3">
+        <v>135200</v>
+      </c>
+      <c r="P49" s="3">
         <v>143700</v>
       </c>
-      <c r="I49" s="3">
-        <v>140000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>142800</v>
-      </c>
-      <c r="K49" s="3">
-        <v>136400</v>
-      </c>
-      <c r="L49" s="3">
-        <v>136300</v>
-      </c>
-      <c r="M49" s="3">
-        <v>135200</v>
-      </c>
-      <c r="N49" s="3">
-        <v>143700</v>
-      </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>149900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>143600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>142300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>146500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>146900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>141800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>128200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>122900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>113600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>117300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>95900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>92400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>90600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>102200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>96900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>87500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>86800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>86400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>79700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4502,8 +4734,14 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4600,106 +4838,118 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>257500</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>257900</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>269300</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>270400</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>243000</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>258400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>272200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>259100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>201100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>237500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>249100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>254400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>181500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>232400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>260800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>290100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>280100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>304600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>339800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>338700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>304900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>273800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>279400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>276600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>301500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>261900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>263500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>260800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>190200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>240400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>259000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4796,106 +5046,118 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6993500</v>
+        <v>6811300</v>
       </c>
       <c r="E54" s="3">
-        <v>6852700</v>
+        <v>6047700</v>
       </c>
       <c r="F54" s="3">
-        <v>6865800</v>
+        <v>6512200</v>
       </c>
       <c r="G54" s="3">
-        <v>6827100</v>
+        <v>6847100</v>
       </c>
       <c r="H54" s="3">
-        <v>6627600</v>
+        <v>6474300</v>
       </c>
       <c r="I54" s="3">
+        <v>6650500</v>
+      </c>
+      <c r="J54" s="3">
+        <v>7032300</v>
+      </c>
+      <c r="K54" s="3">
         <v>6834100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>6959700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>6541000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>6214200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>6072400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>6118800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>6430100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5899200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5934500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>6126200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>6997500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>7000600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>7417000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>7334000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>7436800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>7861200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>7611600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>7576800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>7275300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>7310000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>7429200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>7158200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>6878900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>6653600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>6523700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>6038700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4930,8 +5192,10 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4966,596 +5230,634 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>914300</v>
+        <v>900600</v>
       </c>
       <c r="E57" s="3">
-        <v>899900</v>
+        <v>834600</v>
       </c>
       <c r="F57" s="3">
-        <v>894300</v>
+        <v>851400</v>
       </c>
       <c r="G57" s="3">
-        <v>882200</v>
+        <v>899200</v>
       </c>
       <c r="H57" s="3">
-        <v>890400</v>
+        <v>843300</v>
       </c>
       <c r="I57" s="3">
+        <v>859400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>943400</v>
+      </c>
+      <c r="K57" s="3">
         <v>937300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>869400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>871200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>849800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>810900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>773200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>886600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>818900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>769800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>721600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>816700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>983100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1079200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1034700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1115500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1263000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1184200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1167500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1124900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1124500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1078800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1043900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>979900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>958700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>933000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>807800</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1251300</v>
+        <v>1242900</v>
       </c>
       <c r="E58" s="3">
-        <v>1350100</v>
+        <v>1137400</v>
       </c>
       <c r="F58" s="3">
-        <v>1333200</v>
+        <v>1142900</v>
       </c>
       <c r="G58" s="3">
-        <v>1334400</v>
+        <v>1348900</v>
       </c>
       <c r="H58" s="3">
-        <v>2223700</v>
+        <v>1257200</v>
       </c>
       <c r="I58" s="3">
+        <v>1299900</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1273400</v>
+      </c>
+      <c r="K58" s="3">
         <v>1363800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1381900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1237100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1132500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1068800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>995600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1196900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>957400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1148400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1208100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1331600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1119500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1255200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1143000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1057800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1025500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1002200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1041000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>992900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>2011900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1069900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1039900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1186800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>889700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>906300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>901000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>680700</v>
+        <v>657600</v>
       </c>
       <c r="E59" s="3">
-        <v>596400</v>
+        <v>622200</v>
       </c>
       <c r="F59" s="3">
-        <v>623200</v>
+        <v>656100</v>
       </c>
       <c r="G59" s="3">
-        <v>628200</v>
+        <v>595900</v>
       </c>
       <c r="H59" s="3">
-        <v>1157700</v>
+        <v>587600</v>
       </c>
       <c r="I59" s="3">
+        <v>611900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>649500</v>
+      </c>
+      <c r="K59" s="3">
         <v>598600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>597200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>549600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>539000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>514400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>506000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>502700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>458500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>522400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>488300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>705500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>713500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>722800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>787200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>823100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>898400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>799400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>795000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>858300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>810600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>729400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>698800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>655700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>753700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>634400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>607500</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2846300</v>
+        <v>2801000</v>
       </c>
       <c r="E60" s="3">
-        <v>2846400</v>
+        <v>2594200</v>
       </c>
       <c r="F60" s="3">
-        <v>2850700</v>
+        <v>2650500</v>
       </c>
       <c r="G60" s="3">
-        <v>2844800</v>
+        <v>2844000</v>
       </c>
       <c r="H60" s="3">
-        <v>2705300</v>
+        <v>2688100</v>
       </c>
       <c r="I60" s="3">
+        <v>2771200</v>
+      </c>
+      <c r="J60" s="3">
+        <v>2866300</v>
+      </c>
+      <c r="K60" s="3">
         <v>2899600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2848400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2657900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2521300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2394100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2274800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2586200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2234800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2440600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2418100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2853900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2816100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3057300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2964900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2996400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>3186900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2985700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>3003400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2976100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2986200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2878200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2782600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2822400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>2602100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>2473700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>2316200</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1226100</v>
+        <v>1071200</v>
       </c>
       <c r="E61" s="3">
-        <v>1155600</v>
+        <v>921200</v>
       </c>
       <c r="F61" s="3">
-        <v>1105400</v>
+        <v>1141700</v>
       </c>
       <c r="G61" s="3">
-        <v>1097400</v>
+        <v>1154600</v>
       </c>
       <c r="H61" s="3">
-        <v>1186400</v>
+        <v>1042300</v>
       </c>
       <c r="I61" s="3">
+        <v>1069000</v>
+      </c>
+      <c r="J61" s="3">
+        <v>1162600</v>
+      </c>
+      <c r="K61" s="3">
         <v>1102000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1171100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1175200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1199900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1169700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1179800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1145000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1157000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>970100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1031400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1194200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1163200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1124300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1156800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1249500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1338700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1430100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1409800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1282300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1285700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1404900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1393400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1284400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>1350300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>1387100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>1298000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>379100</v>
+        <v>269400</v>
       </c>
       <c r="E62" s="3">
-        <v>504800</v>
+        <v>237500</v>
       </c>
       <c r="F62" s="3">
-        <v>525200</v>
+        <v>159700</v>
       </c>
       <c r="G62" s="3">
-        <v>514700</v>
+        <v>242500</v>
       </c>
       <c r="H62" s="3">
-        <v>446400</v>
+        <v>246000</v>
       </c>
       <c r="I62" s="3">
+        <v>248400</v>
+      </c>
+      <c r="J62" s="3">
+        <v>226000</v>
+      </c>
+      <c r="K62" s="3">
         <v>529400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>561000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>508700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>407600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>478000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>507200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>510600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>439800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>552700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>593100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>643000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>615900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>660700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>664500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>666500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>645700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>603400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>610100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>590600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>578600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>632000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>612200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>605000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>598500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>669800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>648200</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5652,8 +5954,14 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5750,8 +6058,14 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5848,106 +6162,118 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4663900</v>
+        <v>4345400</v>
       </c>
       <c r="E66" s="3">
-        <v>4709300</v>
+        <v>3936500</v>
       </c>
       <c r="F66" s="3">
-        <v>4681700</v>
+        <v>4145100</v>
       </c>
       <c r="G66" s="3">
-        <v>4651800</v>
+        <v>4503000</v>
       </c>
       <c r="H66" s="3">
-        <v>4485900</v>
+        <v>4225700</v>
       </c>
       <c r="I66" s="3">
+        <v>4341600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>4542500</v>
+      </c>
+      <c r="K66" s="3">
         <v>4723600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4841300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4580900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4360200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4271800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4197300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4477200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>4056700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4185300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4272000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4936700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>4883700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>5140700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>5078600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>5201600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>5481200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>5318700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>5331200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>5151200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>5171900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>5232100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>5098300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>4997900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>4820100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>4780100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>4492300</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5982,8 +6308,10 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6080,8 +6408,14 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6178,8 +6512,14 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6276,8 +6616,14 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6374,106 +6720,118 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1369300</v>
+        <v>1223200</v>
       </c>
       <c r="E72" s="3">
-        <v>1276700</v>
+        <v>1048800</v>
       </c>
       <c r="F72" s="3">
-        <v>1293600</v>
+        <v>1275000</v>
       </c>
       <c r="G72" s="3">
-        <v>1310900</v>
+        <v>1275700</v>
       </c>
       <c r="H72" s="3">
-        <v>1361500</v>
+        <v>1219900</v>
       </c>
       <c r="I72" s="3">
+        <v>1277000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>1420600</v>
+      </c>
+      <c r="K72" s="3">
         <v>1301900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1270000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1190900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1157700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1151000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1235200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1237500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1195000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1165500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1249000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1421000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1454500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1411200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1411100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1371500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1458300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1334100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1231100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1145200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1158300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1164400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1096400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>962100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>922000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>935100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>827300</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6570,8 +6928,14 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6668,8 +7032,14 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6766,106 +7136,118 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2329700</v>
+        <v>2259800</v>
       </c>
       <c r="E76" s="3">
-        <v>2143500</v>
+        <v>1920900</v>
       </c>
       <c r="F76" s="3">
-        <v>2184100</v>
+        <v>2169300</v>
       </c>
       <c r="G76" s="3">
-        <v>2175200</v>
+        <v>2141700</v>
       </c>
       <c r="H76" s="3">
-        <v>2141700</v>
+        <v>2059500</v>
       </c>
       <c r="I76" s="3">
+        <v>2118900</v>
+      </c>
+      <c r="J76" s="3">
+        <v>2283400</v>
+      </c>
+      <c r="K76" s="3">
         <v>2110500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2118400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1960100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1854000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1800600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1921500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1952900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1842500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1749200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1854200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2060800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2116900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2276300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>2255400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2235100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2380000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>2292900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>2245600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>2124100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>2138100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>2197100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>2059900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1881000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1833500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>1743600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>1546400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6962,209 +7344,227 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>92500</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-16900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>36100</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>31900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>7500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>35500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>44800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-26500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>21400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>31100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>67600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-8100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-48800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>66800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>89800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>12400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>35100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>20800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>100200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>83500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>60700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>30100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>68100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>134300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>61800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-11700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>108400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7199,106 +7599,114 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>70300</v>
-      </c>
-      <c r="E83" s="3">
-        <v>69800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>68600</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
+        <v>69700</v>
+      </c>
+      <c r="L83" s="3">
+        <v>68100</v>
+      </c>
+      <c r="M83" s="3">
+        <v>62900</v>
+      </c>
+      <c r="N83" s="3">
+        <v>51300</v>
+      </c>
+      <c r="O83" s="3">
+        <v>61700</v>
+      </c>
+      <c r="P83" s="3">
+        <v>61300</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>62600</v>
+      </c>
+      <c r="R83" s="3">
+        <v>54300</v>
+      </c>
+      <c r="S83" s="3">
+        <v>63700</v>
+      </c>
+      <c r="T83" s="3">
+        <v>61200</v>
+      </c>
+      <c r="U83" s="3">
         <v>67900</v>
       </c>
-      <c r="H83" s="3">
-        <v>73600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>69700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>68100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>62900</v>
-      </c>
-      <c r="L83" s="3">
-        <v>51300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>61700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>61300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>62600</v>
-      </c>
-      <c r="P83" s="3">
-        <v>54300</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="V83" s="3">
         <v>63700</v>
       </c>
-      <c r="R83" s="3">
-        <v>61200</v>
-      </c>
-      <c r="S83" s="3">
-        <v>67900</v>
-      </c>
-      <c r="T83" s="3">
-        <v>63700</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>73000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>63500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>66600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>59000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>67200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>58700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>60900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>55800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>60000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>53900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>57200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>49200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>55900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>49800</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7395,8 +7803,14 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7493,8 +7907,14 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7591,8 +8011,14 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7689,8 +8115,14 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7787,31 +8219,37 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -7885,8 +8323,14 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7921,50 +8365,52 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-19053000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-21210000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-18921000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-20335000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-20698000</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-19316000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-20784000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-19927000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-24223000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -8019,8 +8465,14 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8117,8 +8569,14 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8215,31 +8673,37 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -8313,8 +8777,14 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8349,31 +8819,33 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8447,8 +8919,14 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8545,8 +9023,14 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8643,8 +9127,14 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8741,31 +9231,37 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -8839,31 +9335,37 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8937,31 +9439,37 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -9033,6 +9541,12 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>FUWAY</t>
   </si>
@@ -656,156 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -830,86 +833,89 @@
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>1855900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1876100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1754400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1723500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1536700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1647100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1608300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1762400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1528700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1386100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1505900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2099200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2013000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2103900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2072600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2430900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2371300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2291000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2189100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2386100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2222700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2102500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2114700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1839400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1786300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -934,86 +940,89 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>1588100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1606700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1506200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1471500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1328200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1394400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1348400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1477200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1277800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1174100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1270000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1756500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1673400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1754200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1742700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2038100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1933800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1917100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1828800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2011100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1840300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1727900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1665600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1714700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1490900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1461500</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1038,86 +1047,89 @@
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>267700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>269400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>248200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>252000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>208400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>252700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>259800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>285200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>250900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>212000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>235900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>342700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>339600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>349600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>330000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>392800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>437500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>373900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>360400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>375000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>382400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>374600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>367900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>400000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>348500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>324800</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1154,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1258,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1362,8 +1378,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1388,86 +1407,89 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>11600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-11900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>23700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>39500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>12800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>8800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>13100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>6600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>40100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>106500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>22900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>142600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-45100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1514,8 @@
       <c r="J15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1570,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1605,8 +1630,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1631,86 +1657,89 @@
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>1853400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1853900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1744000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1684600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1560700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1617400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1568500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1721300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1515700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1415200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1556000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2039100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1980600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2063200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2034200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2373600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2244000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2208700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2114500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2388300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2141400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2002700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1941400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2125400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1701300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1727500</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1735,86 +1764,89 @@
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>2500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>22100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>38900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>29700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>39700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>41100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-29100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-50100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>60100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>32400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>40700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>38400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>57300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>127300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>82300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>74600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>81300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>99800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>92100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-10700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>138000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1851,8 +1883,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1877,86 +1910,89 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>69600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>16400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>51400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>31800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>13600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>15700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>21900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>69000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-15600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>162100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>87400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>18700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>27000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>10700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>10500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>25200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>11600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-15400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>13300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>36300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>75200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>6100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>13000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1981,86 +2017,89 @@
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3">
         <v>141800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>106600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>124600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>122000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>51300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>106600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>124200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>164400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>78200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>16500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>179900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>211200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>124100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>131200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>115700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>126800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>219700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>152600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>120100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>66900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>177600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>228900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>155400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>51500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>212000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>117100</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2085,86 +2124,89 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>12000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>5800</v>
       </c>
       <c r="Q22" s="3">
         <v>5800</v>
       </c>
       <c r="R22" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="S22" s="3">
         <v>6200</v>
       </c>
       <c r="T22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="U22" s="3">
         <v>7500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>10400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>8500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8900</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>9200</v>
       </c>
       <c r="AF22" s="3">
         <v>9200</v>
       </c>
       <c r="AG22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AH22" s="3">
         <v>8700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>7300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2189,86 +2231,89 @@
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>60200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>29000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>54900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>64700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>39500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>55800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>103900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-52200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>104300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>138700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>41100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>57300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>39000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>57400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>142400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>84800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>50700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>108400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>165800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>89500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>148700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2293,86 +2338,89 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>24200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>19400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>21000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>32600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-5200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>34400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>44600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>22400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>18700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>20100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-50000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>49000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>16600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>14000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>29400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>24400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>20700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-8200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>30600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2475,8 +2523,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2501,86 +2552,89 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>35900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>35400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>52700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-20600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>25800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>34800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>71300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-47000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>69900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>94200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>18700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>38600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>18800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>107400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>93400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>68200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>36700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>79000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>141400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>68700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>118000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2605,86 +2659,89 @@
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>31900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>35500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>44800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-26500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>21400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>31100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>67600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-48800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>66800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>89800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>12400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>35100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>20800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>100200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>83500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>60700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>30100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>68100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>134300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>61800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-11700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>108400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2787,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2813,8 +2873,8 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2891,8 +2951,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2995,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3099,8 +3165,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3125,86 +3194,89 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-69600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-16400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-51400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-31800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-13600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-21900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-69000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>15600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-162100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-87400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-18700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-10700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-25200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-11600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>15400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-36300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-75200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3229,86 +3301,89 @@
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>31900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>35500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>44800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-26500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>21400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>31100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>67600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-48800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>66800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>89800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>12400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>35100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>20800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>100200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>83500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>60700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>30100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>68100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>134300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>61800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-11700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>108400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3411,8 +3486,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3437,195 +3515,201 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>31900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>35500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>44800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-26500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>21400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>31100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>67600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-48800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>66800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>89800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>12400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>35100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>20800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>100200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>83500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>60700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>30100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>68100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>134300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>61800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-11700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>108400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3662,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3700,112 +3785,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>340300</v>
+      </c>
+      <c r="E41" s="3">
         <v>361200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>270300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>323300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>347200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>360400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>385800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>356800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>414600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>438900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>395800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>432600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>442300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>385500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>641400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>598100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>559200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>637100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>962100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>478900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>346200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>368300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>395300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>428900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>442600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>445400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>374100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>457700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>471100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>479700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>390800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>418400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>496400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>415700</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3813,74 +3902,74 @@
         <v>38000</v>
       </c>
       <c r="E42" s="3">
+        <v>38000</v>
+      </c>
+      <c r="F42" s="3">
         <v>25300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>31400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>29000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>20400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>38600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>27000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>27300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>21100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>21600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>21500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>23600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>24700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>20700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>17100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>16500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>14000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>7900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>14100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>9300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>7400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>22800</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
-      </c>
       <c r="AB42" s="3">
         <v>0</v>
       </c>
@@ -3891,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="AE42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AF42" s="3">
         <v>300</v>
@@ -3900,744 +3989,768 @@
         <v>300</v>
       </c>
       <c r="AH42" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI42" s="3">
         <v>500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1656600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1715900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1534800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1616500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1597800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1512000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1567300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1716300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1577100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1624800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1570000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1522400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1432200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1442100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1466200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1354400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1299400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1221000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1336000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1685000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1802000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1774400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1859900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2097400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2044600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2030100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1984900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2017000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2008900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1887000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1815800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1753000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1623600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1499600</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1280200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1370400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1244600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1214100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1378200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1256500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1289400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1296100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1372500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1293200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1230900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1089700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1066000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1058500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1015000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>856700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>883600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>922000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1042700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1020700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1206600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1150600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1183100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1181000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1242300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1166900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1121800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1028700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1110200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1068000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1019900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>925600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>931400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>806700</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>230200</v>
+      </c>
+      <c r="E45" s="3">
         <v>251900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>236100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>237900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>271400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>247300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>265300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>254300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>270700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>251100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>257300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>273300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>252700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>225300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>270600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>217300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>224200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>204200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>248500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>209700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>250700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>245100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>262500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>311100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>260100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>243600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>229600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>348700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>316300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>301900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>300800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>294400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>325300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3545300</v>
+      </c>
+      <c r="E46" s="3">
         <v>3737500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3311100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3423100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3623600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3396600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3522700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3662100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3661900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3635500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3475100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3339700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3214700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3135000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3417800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3047400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2983400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3000900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3603300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3402200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3619700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3547700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3708100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4041100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3989700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3885900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3710500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3762400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3906800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3736800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3527600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3391900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3377000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3043500</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>943100</v>
+      </c>
+      <c r="E47" s="3">
         <v>956200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>799600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1056200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1076800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1024500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1027400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1121300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>877500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>912200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>834500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>809700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>755600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>772500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>768500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>777300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>789400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>774300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>838300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>936800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1090200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1066100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1062600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1193700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1158400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1237500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1200800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1239600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1221900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1137400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1096400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1162400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1059900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>986800</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1758400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1911300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1751200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1842200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1939600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1855000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1895600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2025700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1896300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1997000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1835900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1727500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1729400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1818500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1839500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1749400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1786900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1943800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2118900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2239700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2274300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2257400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2213800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2204100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2093800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2081600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1996800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1959200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1941700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1933000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1907300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1822700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1766700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>128200</v>
+      </c>
+      <c r="E49" s="3">
         <v>139800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>123800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>134100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>140000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>132500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>138900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>152200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>140000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>142800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>136400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>136300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>135200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>143700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>149900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>143600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>142300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>146500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>146900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>141800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>128200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>122900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>113600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>117300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>95900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>92400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>90600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>102200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>96900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>87500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>86800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>86400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>79700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4740,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4844,8 +4960,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4871,85 +4990,88 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>258400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>272200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>259100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>201100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>237500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>249100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>254400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>181500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>232400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>260800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>290100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>280100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>304600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>339800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>338700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>304900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>273800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>279400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>276600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>301500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>261900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>263500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>260800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>190200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>240400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>259000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5052,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6435600</v>
+      </c>
+      <c r="E54" s="3">
         <v>6811300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6047700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6512200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6847100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6474300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6650500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7032300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6834100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6959700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6541000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6214200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6072400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6118800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6430100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5899200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5934500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6126200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6997500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7000600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7417000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7334000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7436800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7861200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7611600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7576800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7275300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7310000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7429200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7158200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6878900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6653600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6523700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6038700</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5194,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5232,632 +5361,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>866400</v>
+      </c>
+      <c r="E57" s="3">
         <v>900600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>834600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>851400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>899200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>843300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>859400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>943400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>937300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>869400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>871200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>849800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>810900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>773200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>886600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>818900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>769800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>721600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>816700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>983100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1079200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1034700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1115500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1263000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1184200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1167500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1124900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1124500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1078800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1043900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>979900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>958700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>933000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>807800</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1140800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1242900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1137400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1142900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1348900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1257200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1299900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1273400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1363800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1381900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1237100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1132500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1068800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>995600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1196900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>957400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1148400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1208100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1331600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1119500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1255200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1143000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1057800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1025500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1002200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1041000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>992900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2011900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1069900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1039900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1186800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>889700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>906300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>901000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>606100</v>
+      </c>
+      <c r="E59" s="3">
         <v>657600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>622200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>656100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>595900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>587600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>611900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>649500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>598600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>597200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>549600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>539000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>514400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>506000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>502700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>458500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>522400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>488300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>705500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>713500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>722800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>787200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>823100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>898400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>799400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>795000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>858300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>810600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>729400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>698800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>655700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>753700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>634400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>607500</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2613400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2801000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2594200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2650500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2844000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2688100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2771200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2866300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2899600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2848400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2657900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2521300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2394100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2274800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2586200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2234800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2440600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2418100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2853900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2816100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3057300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2964900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2996400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3186900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2985700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3003400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2976100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2986200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2878200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2782600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2822400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2602100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2473700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2316200</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1047500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1071200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>921200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1141700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1154600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1042300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1069000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1162600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1102000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1171100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1175200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1199900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1169700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1179800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1145000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1157000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>970100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1031400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1194200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1163200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1124300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1156800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1249500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1338700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1430100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1409800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1282300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1285700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1404900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1393400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1284400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1350300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1387100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1298000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>299800</v>
+      </c>
+      <c r="E62" s="3">
         <v>269400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>237500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>159700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>242500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>246000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>248400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>226000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>529400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>561000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>508700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>407600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>478000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>507200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>510600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>439800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>552700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>593100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>643000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>615900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>660700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>664500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>666500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>645700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>603400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>610100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>590600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>578600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>632000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>612200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>605000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>598500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>669800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>648200</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5960,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6064,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6168,112 +6322,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4148400</v>
+      </c>
+      <c r="E66" s="3">
         <v>4345400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3936500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4145100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4503000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4225700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4341600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4542500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4723600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4841300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4580900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4360200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4271800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4197300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4477200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4056700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4185300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4272000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4936700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4883700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5140700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5078600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5201600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5481200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5318700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5331200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5151200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5171900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5232100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5098300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4997900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4820100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4780100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4492300</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6310,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6414,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6518,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6622,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6726,112 +6896,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1147900</v>
+      </c>
+      <c r="E72" s="3">
         <v>1223200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1048800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1275000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1275700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1219900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1277000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1420600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1301900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1270000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1190900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1157700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1151000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1235200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1237500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1195000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1165500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1249000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1421000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1454500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1411200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1411100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1371500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1458300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1334100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1231100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1145200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1158300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1164400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1096400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>962100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>922000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>935100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>827300</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6934,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7038,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7142,112 +7324,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2087900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2259800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1920900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2169300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2141700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2059500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2118900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2283400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2110500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2118400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1960100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1854000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1800600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1921500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1952900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1842500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1749200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1854200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2060800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2116900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2276300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2255400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2235100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2380000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2292900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2245600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2124100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2138100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2197100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2059900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1881000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1833500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1743600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1546400</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7350,117 +7538,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7485,86 +7679,89 @@
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>31900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>35500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>44800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-26500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>21400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>31100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>67600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-48800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>66800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>89800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>12400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>35100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>20800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>100200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>83500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>60700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>30100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>68100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>134300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>61800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-11700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>108400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7601,8 +7798,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7627,86 +7825,89 @@
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
         <v>69700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>68100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>62900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>51300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>61700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>61300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>62600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>54300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>63700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>61200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>67900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>63700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>73000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>63500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>66600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>59000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>67200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>58700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>60900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>55800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>60000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>53900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>57200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>49200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>55900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>49800</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7809,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7913,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8017,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8121,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8225,8 +8438,11 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8251,8 +8467,8 @@
       <c r="J89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -8329,8 +8545,11 @@
       <c r="AJ89" s="3">
         <v>0</v>
       </c>
+      <c r="AK89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8367,8 +8586,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8393,27 +8613,27 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-19316000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20784000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-19927000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-24223000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -8471,8 +8691,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8575,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8679,8 +8905,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8705,8 +8934,8 @@
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -8783,8 +9012,11 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8821,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8847,8 +9080,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8925,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9029,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9133,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9237,8 +9479,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9263,8 +9508,8 @@
       <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -9341,8 +9586,11 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9367,8 +9615,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9445,8 +9693,11 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9471,8 +9722,8 @@
       <c r="J102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -9547,6 +9798,9 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
   <si>
     <t>FUWAY</t>
   </si>
@@ -656,159 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -836,86 +840,89 @@
       <c r="K8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>1855900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1876100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1754400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1723500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1536700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1647100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1608300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1762400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1528700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1386100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1505900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2099200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2013000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2103900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2072600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2430900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2371300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2291000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2189100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2386100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2222700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2102500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2114700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1839400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1786300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -943,86 +950,89 @@
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>1588100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1606700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1506200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1471500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1328200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1394400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1348400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1477200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1277800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1174100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1270000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1756500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1673400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1754200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1742700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2038100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1933800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1917100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1828800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2011100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1840300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1727900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1665600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1714700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1490900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1461500</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1050,86 +1060,89 @@
       <c r="K10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>267700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>269400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>248200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>252000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>208400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>252700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>259800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>285200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>250900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>212000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>235900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>342700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>339600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>349600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>330000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>392800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>437500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>373900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>360400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>375000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>382400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>374600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>367900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>400000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>348500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>324800</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,8 +1180,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1274,8 +1288,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,8 +1398,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1410,86 +1430,89 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>11600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-4700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-11900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>23700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>12800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>39500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>12800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>8800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>13100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>6600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>40100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>106500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>22900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>142600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-45100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,8 @@
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1595,8 +1618,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,8 +1657,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1660,86 +1687,89 @@
       <c r="K17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>1853400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1853900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1744000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1684600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1560700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1617400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1568500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1721300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1515700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1415200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1556000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2039100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1980600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2063200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2034200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2373600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2244000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2208700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2114500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2388300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2141400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2002700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1941400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2125400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1701300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1727500</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1767,86 +1797,89 @@
       <c r="K18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>2500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>22100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>38900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>29700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>39700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>41100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-29100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-50100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>60100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>32400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>40700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>38400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>57300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>127300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>82300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>74600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>81300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>99800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>92100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-10700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>138000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,8 +1917,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1913,86 +1947,89 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>69600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>16400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>51400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>31800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>13600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>15700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>21900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>69000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-15600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>162100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>87400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>18700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>27000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>10700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>10500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>25200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>11600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-15400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>13300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>36300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>75200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>6100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>13000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>18100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2020,86 +2057,89 @@
       <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>141800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>106600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>124600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>122000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>51300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>106600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>124200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>164400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>78200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>16500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>179900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>211200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>124100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>131200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>115700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>126800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>219700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>152600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>120100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>66900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>177600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>228900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>155400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>51500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>212000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>117100</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2127,86 +2167,89 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>12000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>5800</v>
       </c>
       <c r="R22" s="3">
         <v>5800</v>
       </c>
       <c r="S22" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="T22" s="3">
         <v>6200</v>
       </c>
       <c r="U22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="V22" s="3">
         <v>7500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8900</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>9200</v>
       </c>
       <c r="AG22" s="3">
         <v>9200</v>
       </c>
       <c r="AH22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AI22" s="3">
         <v>8700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>7400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2234,86 +2277,89 @@
       <c r="K23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>60200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>29000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>54900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>64700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>39500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>55800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>103900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-52200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>104300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>138700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>41100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>57300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>39000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>57400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>142400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>84800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>50700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>108400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>165800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>89500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>148700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2341,86 +2387,89 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>24200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>19300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>13800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>21000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>32600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-5200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>34400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>44600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>22400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>18700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>20100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-50000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>49000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>16600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>14000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>29400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>24400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>20700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-8200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>30600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,8 +2575,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2555,86 +2607,89 @@
       <c r="K26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>35900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>35400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>52700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>25800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>34800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>71300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-47000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>69900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>94200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>18700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>38600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>18800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>107400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>93400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>68200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>36700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>79000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>141400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>68700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>118000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2662,86 +2717,89 @@
       <c r="K27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>31900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>35500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>44800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>21400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>67600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-48800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>66800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>89800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>12400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>35100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>20800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>100200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>83500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>60700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>30100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>68100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>134300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>61800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-11700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>108400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2876,8 +2937,8 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2954,8 +3015,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,8 +3235,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3197,86 +3267,89 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-69600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-16400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-51400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-31800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-15700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-21900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-69000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>15600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-162100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-87400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-18700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-27000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-25200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-11600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>15400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-13300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-36300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-75200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3304,86 +3377,89 @@
       <c r="K33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>31900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>35500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>44800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>21400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>31100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>67600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-48800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>66800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>89800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>12400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>35100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>20800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>100200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>83500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>60700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>30100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>68100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>134300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>61800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-11700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>108400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,8 +3565,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3518,198 +3597,204 @@
       <c r="K35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>31900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>35500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>44800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>21400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>31100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>67600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-48800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>66800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>89800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>12400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>35100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>20800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>100200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>83500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>60700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>30100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>68100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>134300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>61800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-11700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>108400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,193 +3872,197 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>400500</v>
+      </c>
+      <c r="E41" s="3">
         <v>340300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>361200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>270300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>323300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>347200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>360400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>385800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>356800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>414600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>438900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>395800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>432600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>442300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>385500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>641400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>598100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>559200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>637100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>962100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>478900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>346200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>368300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>395300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>428900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>442600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>445400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>374100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>457700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>471100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>479700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>390800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>418400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>496400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>415700</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>38000</v>
+        <v>45500</v>
       </c>
       <c r="E42" s="3">
         <v>38000</v>
       </c>
       <c r="F42" s="3">
+        <v>38000</v>
+      </c>
+      <c r="G42" s="3">
         <v>25300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>31400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>29000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>20400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>14900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>38600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>27000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>27300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>21100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>21600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>21500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>23600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>24700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>20700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>17100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>16500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>14000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>7900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>14100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>9300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>7400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>22800</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
-      </c>
       <c r="AC42" s="3">
         <v>0</v>
       </c>
@@ -3983,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="AF42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AG42" s="3">
         <v>300</v>
@@ -3992,765 +4082,789 @@
         <v>300</v>
       </c>
       <c r="AI42" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>200</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1731700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1656600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1715900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1534800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1616500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1597800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1512000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1567300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1716300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1577100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1624800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1570000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1522400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1432200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1442100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1466200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1354400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1299400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1221000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1336000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1685000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1802000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1774400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1859900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2097400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2044600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2030100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1984900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2017000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2008900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1887000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1815800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1753000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1623600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1499600</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1302500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1280200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1370400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1244600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1214100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1378200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1256500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1289400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1296100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1372500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1293200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1230900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1089700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1066000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1058500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1015000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>856700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>883600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>922000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1042700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1020700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1206600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1150600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1183100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1181000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1242300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1166900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1121800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1028700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1110200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1068000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1019900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>925600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>931400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>806700</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>235700</v>
+      </c>
+      <c r="E45" s="3">
         <v>230200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>251900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>236100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>237900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>271400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>247300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>265300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>254300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>270700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>251100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>257300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>273300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>252700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>225300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>270600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>217300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>224200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>204200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>248500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>209700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>250700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>245100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>262500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>311100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>260100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>243600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>229600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>348700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>316300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>301900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>300800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>294400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>325300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3715800</v>
+      </c>
+      <c r="E46" s="3">
         <v>3545300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3737500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3311100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3423100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3623600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3396600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3522700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3662100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3661900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3635500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3475100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3339700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3214700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3135000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3417800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3047400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2983400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3000900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3603300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3402200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3619700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3547700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3708100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4041100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3989700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3885900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3710500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3762400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3906800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3736800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3527600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3391900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3377000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3043500</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>828000</v>
+      </c>
+      <c r="E47" s="3">
         <v>943100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>956200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>799600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1056200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1076800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1024500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1027400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1121300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>877500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>912200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>834500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>809700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>755600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>772500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>768500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>777300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>789400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>774300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>838300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>936800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1090200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1066100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1062600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1193700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1158400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1237500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1200800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1239600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1221900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1137400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1096400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1162400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1059900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>986800</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1849900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1758400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1911300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1751200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1842200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1939600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1855000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1895600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2025700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1896300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1997000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1835900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1727500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1729400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1818500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1839500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1749400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1786900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1943800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2118900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2239700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2274300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2257400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2213800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2204100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2093800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2081600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1996800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1959200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1941700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1933000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1907300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1822700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1766700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>152700</v>
+      </c>
+      <c r="E49" s="3">
         <v>128200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>139800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>123800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>134100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>140000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>132500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>138900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>152200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>140000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>142800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>136400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>136300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>135200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>143700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>149900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>143600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>142300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>146500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>146900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>141800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>128200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>122900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>113600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>117300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>95900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>92400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>90600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>102200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>96900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>87500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>86800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>86400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>79700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,8 +5080,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4993,85 +5113,88 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>258400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>272200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>259100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>201100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>237500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>249100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>254400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>181500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>232400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>260800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>290100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>280100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>304600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>339800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>338700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>304900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>273800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>279400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>276600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>301500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>261900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>263500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>260800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>190200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>240400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>259000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5300,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6591200</v>
+      </c>
+      <c r="E54" s="3">
         <v>6435600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6811300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6047700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6512200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6847100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6474300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6650500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7032300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6834100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6959700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6541000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6214200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6072400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6118800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6430100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5899200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5934500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6126200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6997500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7000600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7417000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7334000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7436800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7861200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7611600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7576800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7275300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7310000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7429200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7158200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6878900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6653600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6523700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>6038700</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,650 +5492,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>912700</v>
+      </c>
+      <c r="E57" s="3">
         <v>866400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>834600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>851400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>899200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>843300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>859400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>943400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>937300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>869400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>871200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>849800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>810900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>773200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>886600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>818900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>769800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>721600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>816700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>983100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1079200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1034700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1115500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1263000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1184200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1167500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1124900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1124500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1078800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1043900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>979900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>958700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>933000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>807800</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1033700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1140800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1242900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1137400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1142900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1348900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1257200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1299900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1273400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1363800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1381900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1237100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1132500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1068800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>995600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1196900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>957400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1148400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1208100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1331600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1119500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1255200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1143000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1057800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1025500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1002200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1041000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>992900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2011900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1069900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1039900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1186800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>889700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>906300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>901000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>687800</v>
+      </c>
+      <c r="E59" s="3">
         <v>606100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>657600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>622200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>656100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>595900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>587600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>611900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>649500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>598600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>597200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>549600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>539000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>514400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>506000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>502700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>458500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>522400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>488300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>705500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>713500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>722800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>787200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>823100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>898400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>799400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>795000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>858300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>810600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>729400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>698800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>655700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>753700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>634400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>607500</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2634200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2613400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2801000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2594200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2650500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2844000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2688100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2771200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2866300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2899600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2848400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2657900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2521300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2394100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2274800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2586200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2234800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2440600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2418100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2853900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2816100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3057300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2964900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2996400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3186900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2985700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3003400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2976100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2986200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2878200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2782600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2822400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2602100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2473700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2316200</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1094100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1047500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1071200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>921200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1141700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1154600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1042300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1069000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1162600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1102000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1171100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1175200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1199900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1169700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1179800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1145000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1157000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>970100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1031400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1194200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1163200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1124300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1156800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1249500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1338700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1430100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1409800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1282300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1285700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1404900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1393400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1284400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1350300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1387100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1298000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>159100</v>
+      </c>
+      <c r="E62" s="3">
         <v>299800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>269400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>237500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>159700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>242500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>246000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>248400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>226000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>529400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>561000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>508700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>407600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>478000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>507200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>510600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>439800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>552700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>593100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>643000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>615900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>660700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>664500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>666500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>645700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>603400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>610100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>590600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>578600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>632000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>612200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>605000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>598500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>669800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>648200</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6480,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4098100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4148400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4345400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3936500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4145100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4503000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4225700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4341600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4542500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4723600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4841300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4580900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4360200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4271800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4197300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4477200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4056700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4185300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4272000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4936700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4883700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5140700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5078600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5201600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5481200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5318700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5331200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5151200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5171900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5232100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5098300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4997900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4820100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4780100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4492300</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7070,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1327800</v>
+      </c>
+      <c r="E72" s="3">
         <v>1147900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1223200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1048800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1275000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1275700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1219900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1277000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1420600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1301900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1270000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1190900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1157700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1151000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1235200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1237500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1195000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1165500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1249000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1421000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1454500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1411200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1411100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1371500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1458300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1334100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1231100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1145200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1158300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1164400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1096400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>962100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>922000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>935100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>827300</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7510,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2280100</v>
+      </c>
+      <c r="E76" s="3">
         <v>2087900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2259800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1920900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2169300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2141700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2059500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2118900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2283400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2110500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2118400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1960100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1854000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1800600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1921500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1952900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1842500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1749200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1854200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2060800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2116900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2276300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2255400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2235100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2380000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2292900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2245600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2124100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2138100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2197100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2059900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1881000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1833500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1743600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1546400</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,120 +7730,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7682,86 +7877,89 @@
       <c r="K81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>31900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>35500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>44800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>21400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>31100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>67600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-48800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>66800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>89800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>12400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>35100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>20800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>100200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>83500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>60700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>30100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>68100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>134300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>61800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-11700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>108400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,8 +7997,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7828,86 +8027,89 @@
       <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3">
         <v>69700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>68100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>62900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>51300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>61700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>61300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>62600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>54300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>63700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>61200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>67900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>63700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>73000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>63500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>66600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>59000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>67200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>58700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>60900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>55800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>60000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>53900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>57200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>49200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>55900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>49800</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,8 +8655,11 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8470,8 +8687,8 @@
       <c r="K89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -8548,8 +8765,11 @@
       <c r="AK89" s="3">
         <v>0</v>
       </c>
+      <c r="AL89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,8 +8807,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8616,27 +8837,27 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3">
         <v>-19316000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20784000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-19927000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-24223000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -8694,8 +8915,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,8 +9135,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8937,8 +9167,8 @@
       <c r="K94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -9015,8 +9245,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9287,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9083,8 +9317,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9161,8 +9395,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,8 +9725,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9511,8 +9757,8 @@
       <c r="K100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -9589,8 +9835,11 @@
       <c r="AK100" s="3">
         <v>0</v>
       </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9618,8 +9867,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9696,8 +9945,11 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9725,8 +9977,8 @@
       <c r="K102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -9801,6 +10053,9 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FUWAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="92">
   <si>
     <t>FUWAY</t>
   </si>
@@ -656,163 +656,167 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -843,86 +847,89 @@
       <c r="L8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>1855900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1876100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1754400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1723500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1536700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1647100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1608300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1762400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1528700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1386100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1505900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2099200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2013000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2103900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2072600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2430900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2371300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2291000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2189100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2386100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2222700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2102500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2114700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1839400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1786300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -953,86 +960,89 @@
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>1588100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1606700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1506200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1471500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1328200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1394400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1348400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1477200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1277800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1174100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1270000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1756500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1673400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1754200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1742700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2038100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1933800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1917100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1828800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2011100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1840300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1727900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1665600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1714700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1490900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1461500</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1063,86 +1073,89 @@
       <c r="L10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>267700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>269400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>248200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>252000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>208400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>252700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>259800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>285200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>250900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>212000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>235900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>342700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>339600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>349600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>330000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>392800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>437500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>373900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>360400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>375000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>382400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>374600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>367900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>400000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>348500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>324800</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,8 +1194,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1291,8 +1305,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,8 +1418,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1433,86 +1453,89 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>11600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-4700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-11900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>23700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>12800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>39500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>12800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>8800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>13100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>6600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>40100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>106500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>22900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>142600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-45100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1543,8 +1566,8 @@
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1621,8 +1644,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,8 +1684,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1690,86 +1717,89 @@
       <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>1853400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1853900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1744000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1684600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1560700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1617400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1568500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1721300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1515700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1415200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1556000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2039100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1980600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2063200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2034200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2373600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2244000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2208700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2114500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2388300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2141400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2002700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1941400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2125400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1701300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1727500</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1800,86 +1830,89 @@
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>2500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>22100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>38900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>29700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>39700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>41100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-29100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-50100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>60100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>32400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>40700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>38400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>57300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>127300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>82300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>74600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>81300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>99800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>92100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-10700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>138000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,8 +1951,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1950,86 +1984,89 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>69600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>16400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>51400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>31800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>13600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>15700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>21900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>69000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-15600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>162100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>87400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>18700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>27000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>10700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>10500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>25200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>11600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-15400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>13300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>36300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>75200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>13000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>18100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2060,86 +2097,89 @@
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>141800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>106600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>124600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>122000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>51300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>106600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>124200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>164400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>78200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>16500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>179900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>211200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>124100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>131200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>115700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>126800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>219700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>152600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>120100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>66900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>177600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>228900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>155400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>51500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>212000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>117100</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2170,86 +2210,89 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>12000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>5800</v>
       </c>
       <c r="S22" s="3">
         <v>5800</v>
       </c>
       <c r="T22" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="U22" s="3">
         <v>6200</v>
       </c>
       <c r="V22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="W22" s="3">
         <v>7500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>7700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>8800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>9900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8900</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>9200</v>
       </c>
       <c r="AH22" s="3">
         <v>9200</v>
       </c>
       <c r="AI22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>7300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>7400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2280,86 +2323,89 @@
       <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>60200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>29000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>54900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>64700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>39500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>55800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>103900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-52200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>104300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>138700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>41100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>57300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>39000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>57400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>142400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>84800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>50700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>108400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>165800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>89500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>148700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2390,86 +2436,89 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>24200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>19400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>12000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>21000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>32600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-5200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>34400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>44600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>22400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>18700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>20100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-50000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>49000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>16600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>14000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>29400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>24400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>20700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-8200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>30600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,8 +2627,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2610,86 +2662,89 @@
       <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>35900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>35400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>52700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>25800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>34800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>71300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-47000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>69900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>94200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>18700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>38600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>18800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>107400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>93400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>68200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>36700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>79000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>141400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>68700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>118000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2720,86 +2775,89 @@
       <c r="L27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>31900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>35500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>44800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-26500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>21400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>67600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-48800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>66800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>89800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>12400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>35100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>20800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>100200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>83500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>60700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>30100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>68100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>134300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>61800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-11700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>108400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,8 +2966,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2940,8 +3001,8 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -3018,8 +3079,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3192,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,8 +3305,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3270,86 +3340,89 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>-69600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-16400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-51400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-31800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-13600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-15700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-21900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-69000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>15600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-162100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-87400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-18700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-27000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-25200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-11600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>15400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-36300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-75200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3380,86 +3453,89 @@
       <c r="L33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>31900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>35500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>44800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-26500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>21400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>31100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>67600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-48800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>66800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>89800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>12400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>35100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>20800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>100200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>83500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>60700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>30100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>68100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>134300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>61800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-11700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>108400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,8 +3644,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3600,201 +3679,207 @@
       <c r="L35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>31900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>35500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>44800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-26500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>21400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>31100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>67600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-48800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>66800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>89800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>12400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>35100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>20800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>100200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>83500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>60700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>30100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>68100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>134300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>61800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-11700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>108400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3918,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,199 +3959,203 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
         <v>400500</v>
       </c>
-      <c r="E41" s="3">
-        <v>340300</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="3">
         <v>361200</v>
       </c>
-      <c r="G41" s="3">
-        <v>270300</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3">
         <v>323300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>347200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>360400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>385800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>356800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>414600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>438900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>395800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>432600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>442300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>385500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>641400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>598100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>559200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>637100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>962100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>478900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>346200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>368300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>395300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>428900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>442600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>445400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>374100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>457700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>471100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>479700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>390800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>418400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>496400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>415700</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>45500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>38000</v>
       </c>
-      <c r="F42" s="3">
-        <v>38000</v>
-      </c>
-      <c r="G42" s="3">
-        <v>25300</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>31400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>29000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>20400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>14900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>38600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>27000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>27300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>21100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>21600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>21500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>23600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>24700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>20700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>17100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>16500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>14000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>7900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>14100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>9300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>7400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>22800</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
       <c r="AD42" s="3">
         <v>0</v>
       </c>
@@ -4076,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="AG42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AH42" s="3">
         <v>300</v>
@@ -4085,786 +4175,810 @@
         <v>300</v>
       </c>
       <c r="AJ42" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK42" s="3">
         <v>500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>200</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
         <v>1731700</v>
       </c>
-      <c r="E43" s="3">
-        <v>1656600</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
         <v>1715900</v>
       </c>
-      <c r="G43" s="3">
-        <v>1534800</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3">
         <v>1616500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1597800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1512000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1567300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1716300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1577100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1624800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1570000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1522400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1432200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1442100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1466200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1354400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1299400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1221000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1336000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1685000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1802000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1774400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1859900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2097400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2044600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2030100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1984900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2017000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2008900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1887000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1815800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1753000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1623600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1499600</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>1302500</v>
       </c>
-      <c r="E44" s="3">
-        <v>1280200</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3">
         <v>1370400</v>
       </c>
-      <c r="G44" s="3">
-        <v>1244600</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3">
         <v>1214100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1378200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1256500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1289400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1296100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1372500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1293200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1230900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1089700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1066000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1058500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1015000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>856700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>883600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>922000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1042700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1020700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1206600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1150600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1183100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1181000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1242300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1166900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1121800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1028700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1110200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1068000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1019900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>925600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>931400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>806700</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>235700</v>
       </c>
-      <c r="E45" s="3">
-        <v>230200</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>251900</v>
       </c>
-      <c r="G45" s="3">
-        <v>236100</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>237900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>271400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>247300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>265300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>254300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>270700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>251100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>257300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>273300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>252700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>225300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>270600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>217300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>224200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>204200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>248500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>209700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>250700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>245100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>262500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>311100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>260100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>243600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>229600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>348700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>316300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>301900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>300800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>294400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>325300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>321100</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
         <v>3715800</v>
       </c>
-      <c r="E46" s="3">
-        <v>3545300</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3">
         <v>3737500</v>
       </c>
-      <c r="G46" s="3">
-        <v>3311100</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3">
         <v>3423100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3623600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3396600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3522700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3662100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3661900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3635500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3475100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3339700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3214700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3135000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3417800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3047400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2983400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3000900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3603300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3402200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3619700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3547700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3708100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4041100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3989700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3885900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3710500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3762400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3906800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3736800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3527600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3391900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3377000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3043500</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>828000</v>
       </c>
-      <c r="E47" s="3">
-        <v>943100</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>956200</v>
       </c>
-      <c r="G47" s="3">
-        <v>799600</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>1056200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1076800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1024500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1027400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1121300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>877500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>912200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>834500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>809700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>755600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>772500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>768500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>777300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>789400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>774300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>838300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>936800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1090200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1066100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1062600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1193700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1158400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1237500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1200800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1239600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1221900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1137400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1096400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1162400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1059900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>986800</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>1849900</v>
       </c>
-      <c r="E48" s="3">
-        <v>1758400</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3">
         <v>1911300</v>
       </c>
-      <c r="G48" s="3">
-        <v>1751200</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3">
         <v>1842200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1939600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1855000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1895600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2025700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1896300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1997000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1835900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1727500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1729400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1818500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1839500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1749400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1786900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1943800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2118900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2239700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2274300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2257400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2213800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2204100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2093800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2081600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1996800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1959200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1941700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1933000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1907300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1822700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1766700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3">
         <v>152700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="3">
+        <v>139800</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3">
+        <v>134100</v>
+      </c>
+      <c r="J49" s="3">
+        <v>140000</v>
+      </c>
+      <c r="K49" s="3">
+        <v>132500</v>
+      </c>
+      <c r="L49" s="3">
+        <v>138900</v>
+      </c>
+      <c r="M49" s="3">
+        <v>152200</v>
+      </c>
+      <c r="N49" s="3">
+        <v>140000</v>
+      </c>
+      <c r="O49" s="3">
+        <v>142800</v>
+      </c>
+      <c r="P49" s="3">
+        <v>136400</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>136300</v>
+      </c>
+      <c r="R49" s="3">
+        <v>135200</v>
+      </c>
+      <c r="S49" s="3">
+        <v>143700</v>
+      </c>
+      <c r="T49" s="3">
+        <v>149900</v>
+      </c>
+      <c r="U49" s="3">
+        <v>143600</v>
+      </c>
+      <c r="V49" s="3">
+        <v>142300</v>
+      </c>
+      <c r="W49" s="3">
+        <v>146500</v>
+      </c>
+      <c r="X49" s="3">
+        <v>146900</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>141800</v>
+      </c>
+      <c r="Z49" s="3">
         <v>128200</v>
       </c>
-      <c r="F49" s="3">
-        <v>139800</v>
-      </c>
-      <c r="G49" s="3">
-        <v>123800</v>
-      </c>
-      <c r="H49" s="3">
-        <v>134100</v>
-      </c>
-      <c r="I49" s="3">
-        <v>140000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>132500</v>
-      </c>
-      <c r="K49" s="3">
-        <v>138900</v>
-      </c>
-      <c r="L49" s="3">
-        <v>152200</v>
-      </c>
-      <c r="M49" s="3">
-        <v>140000</v>
-      </c>
-      <c r="N49" s="3">
-        <v>142800</v>
-      </c>
-      <c r="O49" s="3">
-        <v>136400</v>
-      </c>
-      <c r="P49" s="3">
-        <v>136300</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>135200</v>
-      </c>
-      <c r="R49" s="3">
-        <v>143700</v>
-      </c>
-      <c r="S49" s="3">
-        <v>149900</v>
-      </c>
-      <c r="T49" s="3">
-        <v>143600</v>
-      </c>
-      <c r="U49" s="3">
-        <v>142300</v>
-      </c>
-      <c r="V49" s="3">
-        <v>146500</v>
-      </c>
-      <c r="W49" s="3">
-        <v>146900</v>
-      </c>
-      <c r="X49" s="3">
-        <v>141800</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>128200</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>122900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>113600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>117300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>95900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>92400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>90600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>102200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>96900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>87500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>86800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>86400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>79700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5087,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,25 +5200,28 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -5116,85 +5236,88 @@
         <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>258400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>272200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>259100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>201100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>237500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>249100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>254400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>181500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>232400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>260800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>290100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>280100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>304600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>339800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>338700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>304900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>273800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>279400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>276600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>301500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>261900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>263500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>260800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>190200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>240400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>259000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,118 +5426,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
         <v>6591200</v>
       </c>
-      <c r="E54" s="3">
-        <v>6435600</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="3">
         <v>6811300</v>
       </c>
-      <c r="G54" s="3">
-        <v>6047700</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3">
         <v>6512200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6847100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6474300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6650500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7032300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6834100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6959700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6541000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6214200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6072400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6118800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6430100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5899200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5934500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6126200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6997500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7000600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7417000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7334000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7436800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7861200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7611600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7576800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7275300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7310000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7429200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7158200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6878900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6653600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>6523700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>6038700</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5582,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,668 +5623,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>912700</v>
       </c>
-      <c r="E57" s="3">
-        <v>866400</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3">
         <v>900600</v>
       </c>
-      <c r="G57" s="3">
-        <v>834600</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
         <v>851400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>899200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>843300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>859400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>943400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>937300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>869400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>871200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>849800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>810900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>773200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>886600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>818900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>769800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>721600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>816700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>983100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1079200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1034700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1115500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1263000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1184200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1167500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1124900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1124500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1078800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1043900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>979900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>958700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>933000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>807800</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3">
         <v>1033700</v>
       </c>
-      <c r="E58" s="3">
-        <v>1140800</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3">
         <v>1242900</v>
       </c>
-      <c r="G58" s="3">
-        <v>1137400</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3">
         <v>1142900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1348900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1257200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1299900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1273400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1363800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1381900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1237100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1132500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1068800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>995600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1196900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>957400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1148400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1208100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1331600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1119500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1255200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1143000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1057800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1025500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1002200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1041000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>992900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2011900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1069900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1039900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1186800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>889700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>906300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>901000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>687800</v>
       </c>
-      <c r="E59" s="3">
-        <v>606100</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>657600</v>
       </c>
-      <c r="G59" s="3">
-        <v>622200</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>656100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>595900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>587600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>611900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>649500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>598600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>597200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>549600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>539000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>514400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>506000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>502700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>458500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>522400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>488300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>705500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>713500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>722800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>787200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>823100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>898400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>799400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>795000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>858300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>810600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>729400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>698800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>655700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>753700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>634400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>607500</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
         <v>2634200</v>
       </c>
-      <c r="E60" s="3">
-        <v>2613400</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="3">
         <v>2801000</v>
       </c>
-      <c r="G60" s="3">
-        <v>2594200</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3">
         <v>2650500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2844000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2688100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2771200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2866300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2899600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2848400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2657900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2521300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2394100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2274800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2586200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2234800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2440600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2418100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2853900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2816100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3057300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2964900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2996400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3186900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2985700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3003400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2976100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2986200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2878200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2782600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2822400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2602100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2473700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2316200</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>1094100</v>
       </c>
-      <c r="E61" s="3">
-        <v>1047500</v>
-      </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>1071200</v>
       </c>
-      <c r="G61" s="3">
-        <v>921200</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>1141700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1154600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1042300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1069000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1162600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1102000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1171100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1175200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1199900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1169700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1179800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1145000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1157000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>970100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1031400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1194200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1163200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1124300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1156800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1249500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1338700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1430100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1409800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1282300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1285700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1404900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1393400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1284400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1350300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1387100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1298000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3">
         <v>159100</v>
       </c>
-      <c r="E62" s="3">
-        <v>299800</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3">
         <v>269400</v>
       </c>
-      <c r="G62" s="3">
-        <v>237500</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
         <v>159700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>242500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>246000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>248400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>226000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>529400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>561000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>508700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>407600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>478000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>507200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>510600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>439800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>552700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>593100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>643000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>615900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>660700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>664500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>666500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>645700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>603400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>610100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>590600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>578600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>632000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>612200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>605000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>598500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>669800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>648200</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6412,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6525,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,118 +6638,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
         <v>4098100</v>
       </c>
-      <c r="E66" s="3">
-        <v>4148400</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="3">
         <v>4345400</v>
       </c>
-      <c r="G66" s="3">
-        <v>3936500</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3">
         <v>4145100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4503000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4225700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4341600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4542500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4723600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4841300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4580900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4360200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4271800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4197300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4477200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4056700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4185300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4272000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4936700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4883700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5140700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5078600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5201600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5481200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5318700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5331200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5151200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5171900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5232100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5098300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4997900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4820100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4780100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4492300</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6794,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6905,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7018,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6963,8 +7131,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,118 +7244,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>1327800</v>
       </c>
-      <c r="E72" s="3">
-        <v>1147900</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3">
         <v>1223200</v>
       </c>
-      <c r="G72" s="3">
-        <v>1048800</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
         <v>1275000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1275700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1219900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1277000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1420600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1301900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1270000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1190900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1157700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1151000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1235200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1237500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1195000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1165500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1249000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1421000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1454500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1411200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1411100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1371500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1458300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1334100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1231100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1145200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1158300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1164400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1096400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>962100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>922000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>935100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>827300</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7470,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7583,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,118 +7696,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
         <v>2280100</v>
       </c>
-      <c r="E76" s="3">
-        <v>2087900</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="3">
         <v>2259800</v>
       </c>
-      <c r="G76" s="3">
-        <v>1920900</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3">
         <v>2169300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2141700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2059500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2118900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2283400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2110500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2118400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1960100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1854000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1800600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1921500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1952900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1842500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1749200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1854200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2060800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2116900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2276300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2255400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2235100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2380000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2292900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2245600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2124100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2138100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2197100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2059900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1881000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1833500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1743600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1546400</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,123 +7922,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7880,86 +8075,89 @@
       <c r="L81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>31900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>35500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>44800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-26500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>21400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>31100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>67600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-48800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>66800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>89800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>12400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>35100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>20800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>100200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>83500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>60700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>30100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>68100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>134300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>61800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-11700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>108400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,8 +8196,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8030,86 +8229,89 @@
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>69700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>68100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>62900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>51300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>61700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>61300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>62600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>54300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>63700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>61200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>67900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>63700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>73000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>63500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>66600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>59000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>67200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>58700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>60900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>55800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>60000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>53900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>57200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>49200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>55900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>49800</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8420,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8533,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8646,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8759,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,8 +8872,11 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8690,8 +8907,8 @@
       <c r="L89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -8768,8 +8985,11 @@
       <c r="AL89" s="3">
         <v>0</v>
       </c>
+      <c r="AM89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,8 +9028,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8840,27 +9061,27 @@
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" s="3">
         <v>-19316000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20784000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-19927000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-24223000</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -8918,8 +9139,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9252,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,8 +9365,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9170,8 +9400,8 @@
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -9248,8 +9478,11 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,8 +9521,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9320,8 +9554,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9398,8 +9632,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9745,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9858,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,8 +9971,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9760,8 +10006,8 @@
       <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9838,8 +10084,11 @@
       <c r="AL100" s="3">
         <v>0</v>
       </c>
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9870,8 +10119,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9948,8 +10197,11 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9980,8 +10232,8 @@
       <c r="L102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -10056,6 +10308,9 @@
         <v>0</v>
       </c>
       <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>0</v>
       </c>
     </row>
